--- a/CRM_Weekly-report-W12.xlsx
+++ b/CRM_Weekly-report-W12.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30306"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cmcglobalcompany-my.sharepoint.com/personal/nnthinh_cmcglobal_vn/Documents/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="23" documentId="13_ncr:1_{E730E25D-76CA-4DFF-A4F5-AB1F81253294}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E87FD3EB-EF25-40E7-99EC-F5252AD8297B}"/>
+  <xr:revisionPtr revIDLastSave="51" documentId="13_ncr:1_{E730E25D-76CA-4DFF-A4F5-AB1F81253294}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{18073694-DAB9-43C8-B7A4-335638B1CFE3}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-90" windowWidth="29040" windowHeight="15720" tabRatio="638" firstSheet="4" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-90" windowWidth="29040" windowHeight="15720" tabRatio="638" firstSheet="13" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cover" sheetId="18" r:id="rId1"/>
@@ -26,7 +26,7 @@
     <sheet name="W9(15- 18 6)" sheetId="30" r:id="rId11"/>
     <sheet name="W10(22- 26 6)" sheetId="31" r:id="rId12"/>
     <sheet name="W11(29- 03 7)" sheetId="32" r:id="rId13"/>
-    <sheet name="Sheet1" sheetId="33" r:id="rId14"/>
+    <sheet name="W12(06 7- 10 7)" sheetId="34" r:id="rId14"/>
   </sheets>
   <externalReferences>
     <externalReference r:id="rId15"/>
@@ -393,6 +393,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -493,7 +495,7 @@
     <author>Administrator</author>
   </authors>
   <commentList>
-    <comment ref="H15" authorId="0" shapeId="0" xr:uid="{1BF2D2BD-87FD-4DAB-B8D3-B7E8C6CD569B}">
+    <comment ref="J20" authorId="0" shapeId="0" xr:uid="{4255F3F8-1965-409B-AA44-26EDA896165A}">
       <text>
         <r>
           <rPr>
@@ -510,7 +512,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I15" authorId="0" shapeId="0" xr:uid="{A931EFFC-4FDB-40D0-B6FB-65ADBDDAA1B8}">
+    <comment ref="K20" authorId="0" shapeId="0" xr:uid="{67D7A728-D899-4907-A9BF-DB9AEAC2A758}">
       <text>
         <r>
           <rPr>
@@ -884,7 +886,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="721" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="746" uniqueCount="117">
   <si>
     <t>Weekly REPORT</t>
   </si>
@@ -898,18 +900,30 @@
     <t> </t>
   </si>
   <si>
+    <t>G1_DU1.18_Ngân hàng TMCP Công Thương Việt Nam (VietinBank)_T&amp;M</t>
+  </si>
+  <si>
     <t>Mã dự án</t>
   </si>
   <si>
+    <t xml:space="preserve"> P-3892</t>
+  </si>
+  <si>
     <t>Mã vụ việc</t>
   </si>
   <si>
+    <t>GLBOD2600218</t>
+  </si>
+  <si>
     <t>PM</t>
   </si>
   <si>
     <t>Người soạn thảo</t>
   </si>
   <si>
+    <t>Nguyễn Ngọc Thịnh</t>
+  </si>
+  <si>
     <t>Người phê duyệt</t>
   </si>
   <si>
@@ -983,12 +997,24 @@
   </si>
   <si>
     <t xml:space="preserve">Tài liệu này được phân phối hạn chế và không được sử dụng cho bất kỳ mục đích nào khác ngoài mục đích liên quan đến CMC GLOBAL. Nội dung của tài liệu này không được tiết lộ cho bất kỳ bên thứ ba nào khác nếu không có sự cho phép trước bằng văn bản của CMC GLOBAL. </t>
+  </si>
+  <si>
+    <t>Weekly Report W1-2 (21/04-1/5)</t>
+  </si>
+  <si>
+    <t>Project: CRM</t>
+  </si>
+  <si>
+    <t>Reporter: nnthinh@cmcglobal.vn</t>
   </si>
   <si>
     <t>Report Date:</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
+    <t>Receiver: hatitphamthi@gmail.com</t>
+  </si>
+  <si>
     <t>1. Tổng quan tình hình dự án</t>
   </si>
   <si>
@@ -999,6 +1025,9 @@
   </si>
   <si>
     <t>Số lượng nhân sự</t>
+  </si>
+  <si>
+    <t>Flutter</t>
   </si>
   <si>
     <t>2. Tình hình nhân sự và các vấn đề phát sinh trong tuần</t>
@@ -1023,9 +1052,42 @@
     <t>Feedback từ khách hàng</t>
   </si>
   <si>
+    <t>Mobile App Banking</t>
+  </si>
+  <si>
+    <t>Trần Hoàng Hiệp</t>
+  </si>
+  <si>
+    <t>Senior</t>
+  </si>
+  <si>
+    <t>1/1</t>
+  </si>
+  <si>
     <t>Chưa có</t>
   </si>
   <si>
+    <t>Nguyễn Văn An</t>
+  </si>
+  <si>
+    <t>Middle</t>
+  </si>
+  <si>
+    <t>đọc và làm quen với source code trước khi nhận task.</t>
+  </si>
+  <si>
+    <t>Phạm Đức Trường</t>
+  </si>
+  <si>
+    <t>Mai Văn Tuấn</t>
+  </si>
+  <si>
+    <t>Trần Mạnh Huy</t>
+  </si>
+  <si>
+    <t>2/2</t>
+  </si>
+  <si>
     <t>3. Các khó khăn, rủi ro tiềm ẩn chung</t>
   </si>
   <si>
@@ -1050,64 +1112,22 @@
     <t>Chưa phát sinh</t>
   </si>
   <si>
-    <t>Flutter</t>
-  </si>
-  <si>
-    <t>Mobile App Banking</t>
-  </si>
-  <si>
-    <t>Trần Hoàng Hiệp</t>
-  </si>
-  <si>
-    <t>Nguyễn Văn An</t>
-  </si>
-  <si>
-    <t>Phạm Đức Trường</t>
-  </si>
-  <si>
-    <t>Mai Văn Tuấn</t>
-  </si>
-  <si>
-    <t>Trần Mạnh Huy</t>
-  </si>
-  <si>
-    <t>Senior</t>
-  </si>
-  <si>
-    <t>Middle</t>
-  </si>
-  <si>
-    <t>1/1</t>
-  </si>
-  <si>
-    <t>2/2</t>
-  </si>
-  <si>
-    <t>đọc và làm quen với source code trước khi nhận task.</t>
-  </si>
-  <si>
-    <t>Receiver: hatitphamthi@gmail.com</t>
-  </si>
-  <si>
-    <t>Project: CRM</t>
-  </si>
-  <si>
-    <t>Weekly Report W1-2 (21/04-1/5)</t>
-  </si>
-  <si>
-    <t>Reporter: nnthinh@cmcglobal.vn</t>
-  </si>
-  <si>
     <t>Weekly Report W3 (04/04-08/05)</t>
   </si>
   <si>
     <t>3/3</t>
   </si>
   <si>
+    <t> chưa hiểu tài liệu ngay vì thời gian tiếp xúc dự án ngắn</t>
+  </si>
+  <si>
     <t>Do API lỗi nhiều nên chưa ghép hoàn chỉnh được</t>
   </si>
   <si>
-    <t> chưa hiểu tài liệu ngay vì thời gian tiếp xúc dự án ngắn</t>
+    <t>Weekly Report W5 (11/05-15/05)</t>
+  </si>
+  <si>
+    <t>18/5/2026</t>
   </si>
   <si>
     <t>Ngày Onboard</t>
@@ -1119,48 +1139,42 @@
     <t>28/04/2026</t>
   </si>
   <si>
-    <t>Weekly Report W5 (11/05-15/05)</t>
-  </si>
-  <si>
     <t>4/4</t>
   </si>
   <si>
-    <t>18/5/2026</t>
+    <t>Weekly Report W5 (18/05-22/05)</t>
   </si>
   <si>
     <t>25/5/2026</t>
   </si>
   <si>
-    <t>Weekly Report W5 (18/05-22/05)</t>
-  </si>
-  <si>
     <t>Weekly Report W6 (25/05-29/05)</t>
   </si>
   <si>
     <t>Weekly Report W7 (01/06-05/06)</t>
   </si>
   <si>
+    <t>Weekly Report W8 (08/06-12/06)</t>
+  </si>
+  <si>
     <t>16/6/2026</t>
   </si>
   <si>
-    <t>Weekly Report W8 (08/06-12/06)</t>
-  </si>
-  <si>
     <t>Note</t>
   </si>
   <si>
     <t>Thứ 6 (12/6) các nhân sự nghỉ vì teambuilding của CMCG</t>
   </si>
   <si>
+    <t>Weekly Report W9 (15/06-19/06)</t>
+  </si>
+  <si>
+    <t>24/6/2026</t>
+  </si>
+  <si>
     <t>chưa phát sinh</t>
   </si>
   <si>
-    <t>Weekly Report W9 (15/06-19/06)</t>
-  </si>
-  <si>
-    <t>24/6/2026</t>
-  </si>
-  <si>
     <t>Weekly Report W10 (22/06-26/06)</t>
   </si>
   <si>
@@ -1179,22 +1193,52 @@
     <t>Nghỉ thứ 6 ( 03/07)</t>
   </si>
   <si>
-    <t xml:space="preserve"> P-3892</t>
-  </si>
-  <si>
-    <t>GLBOD2600218</t>
-  </si>
-  <si>
-    <t>Nguyễn Ngọc Thịnh</t>
-  </si>
-  <si>
-    <t>G1_DU1.18_Ngân hàng TMCP Công Thương Việt Nam (VietinBank)_T&amp;M</t>
-  </si>
-  <si>
-    <t>Weekly Report W12 (06/07-10/07)</t>
-  </si>
-  <si>
-    <t>13/7/2026</t>
+    <t>Weekly Report  06/07 ~ 10/07</t>
+  </si>
+  <si>
+    <t>15-07-2026</t>
+  </si>
+  <si>
+    <t>1. Kế hoạch load CV</t>
+  </si>
+  <si>
+    <t>Số lượng request</t>
+  </si>
+  <si>
+    <t>Level</t>
+  </si>
+  <si>
+    <t>Số lượng CV đã gửi</t>
+  </si>
+  <si>
+    <t>Số lượng CV passed</t>
+  </si>
+  <si>
+    <t>2. Kế hoạch onboard sắp tới</t>
+  </si>
+  <si>
+    <t>Tên nhân sự</t>
+  </si>
+  <si>
+    <t>Ngày onboard dự kiến</t>
+  </si>
+  <si>
+    <t>Địa điểm onboard</t>
+  </si>
+  <si>
+    <t>Ngõ 8 Hoàng Đạo Thuý</t>
+  </si>
+  <si>
+    <t>2. Tình hình nhân sự đang onborad và các vấn đề phát sinh trong tuần</t>
+  </si>
+  <si>
+    <t>Số giờ OT</t>
+  </si>
+  <si>
+    <t>Tổng số ngày làm việc trong tuần</t>
+  </si>
+  <si>
+    <t>Số ngày đi muộn</t>
   </si>
 </sst>
 </file>
@@ -1207,7 +1251,7 @@
     <numFmt numFmtId="165" formatCode="[$-409]d\-mmm\-yy;@"/>
     <numFmt numFmtId="166" formatCode="0.0"/>
   </numFmts>
-  <fonts count="37">
+  <fonts count="38">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -1447,6 +1491,14 @@
       <family val="1"/>
       <scheme val="major"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Cambria"/>
+      <family val="1"/>
+      <scheme val="major"/>
+    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -1492,7 +1544,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="32">
+  <borders count="34">
     <border>
       <left/>
       <right/>
@@ -1889,6 +1941,32 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -1911,7 +1989,7 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="159">
+  <cellXfs count="180">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2156,6 +2234,27 @@
     </xf>
     <xf numFmtId="0" fontId="34" fillId="4" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="34" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="37" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="10" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="23" fillId="4" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -2231,6 +2330,54 @@
     <xf numFmtId="0" fontId="17" fillId="2" borderId="0" xfId="11" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="4" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="5" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="6" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="4" borderId="7" xfId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="4" borderId="8" xfId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="15" fillId="4" borderId="8" xfId="7" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="15" fillId="4" borderId="8" xfId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="8" xfId="7" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="8" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="8" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="9" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="4" borderId="10" xfId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="4" borderId="1" xfId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="1" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="1" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="11" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="15" fillId="4" borderId="12" xfId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2249,54 +2396,6 @@
     <xf numFmtId="0" fontId="15" fillId="4" borderId="0" xfId="7" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="15" fillId="4" borderId="10" xfId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="15" fillId="4" borderId="1" xfId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="1" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="1" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="11" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="4" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="5" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="6" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="15" fillId="4" borderId="7" xfId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="15" fillId="4" borderId="8" xfId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="15" fillId="4" borderId="8" xfId="7" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="15" fillId="4" borderId="8" xfId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="8" xfId="7" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="8" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="8" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="9" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2306,9 +2405,6 @@
     <xf numFmtId="0" fontId="10" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="29" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2324,9 +2420,6 @@
     <xf numFmtId="0" fontId="29" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2336,8 +2429,56 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="29" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="6" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="13">
@@ -2746,6 +2887,61 @@
         <a:xfrm>
           <a:off x="98778" y="1"/>
           <a:ext cx="806097" cy="619124"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>98778</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>619125</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>111751</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{532900D7-4286-4CAE-BE24-C5AC38C444B4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="98778" y="0"/>
+          <a:ext cx="834672" cy="626101"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3248,58 +3444,58 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:16">
-      <c r="B2" s="100"/>
-      <c r="C2" s="101"/>
-      <c r="D2" s="101"/>
-      <c r="E2" s="106" t="s">
+      <c r="B2" s="107"/>
+      <c r="C2" s="108"/>
+      <c r="D2" s="108"/>
+      <c r="E2" s="113" t="s">
         <v>0</v>
       </c>
-      <c r="F2" s="107"/>
-      <c r="G2" s="107"/>
-      <c r="H2" s="107"/>
-      <c r="I2" s="107"/>
-      <c r="J2" s="107"/>
-      <c r="K2" s="108"/>
-      <c r="L2" s="115"/>
-      <c r="M2" s="116"/>
-      <c r="N2" s="116"/>
-      <c r="O2" s="117"/>
+      <c r="F2" s="114"/>
+      <c r="G2" s="114"/>
+      <c r="H2" s="114"/>
+      <c r="I2" s="114"/>
+      <c r="J2" s="114"/>
+      <c r="K2" s="115"/>
+      <c r="L2" s="122"/>
+      <c r="M2" s="123"/>
+      <c r="N2" s="123"/>
+      <c r="O2" s="124"/>
     </row>
     <row r="3" spans="2:16" ht="14.25" customHeight="1">
-      <c r="B3" s="102"/>
-      <c r="C3" s="103"/>
-      <c r="D3" s="103"/>
-      <c r="E3" s="109"/>
-      <c r="F3" s="110"/>
-      <c r="G3" s="110"/>
-      <c r="H3" s="110"/>
-      <c r="I3" s="110"/>
-      <c r="J3" s="110"/>
-      <c r="K3" s="111"/>
-      <c r="L3" s="118" t="s">
+      <c r="B3" s="109"/>
+      <c r="C3" s="110"/>
+      <c r="D3" s="110"/>
+      <c r="E3" s="116"/>
+      <c r="F3" s="117"/>
+      <c r="G3" s="117"/>
+      <c r="H3" s="117"/>
+      <c r="I3" s="117"/>
+      <c r="J3" s="117"/>
+      <c r="K3" s="118"/>
+      <c r="L3" s="125" t="s">
         <v>1</v>
       </c>
-      <c r="M3" s="119"/>
-      <c r="N3" s="119"/>
-      <c r="O3" s="120"/>
+      <c r="M3" s="126"/>
+      <c r="N3" s="126"/>
+      <c r="O3" s="127"/>
     </row>
     <row r="4" spans="2:16" s="7" customFormat="1" ht="15" customHeight="1">
-      <c r="B4" s="104"/>
-      <c r="C4" s="105"/>
-      <c r="D4" s="105"/>
-      <c r="E4" s="112"/>
-      <c r="F4" s="113"/>
-      <c r="G4" s="113"/>
-      <c r="H4" s="113"/>
-      <c r="I4" s="113"/>
-      <c r="J4" s="113"/>
-      <c r="K4" s="114"/>
-      <c r="L4" s="118" t="s">
+      <c r="B4" s="111"/>
+      <c r="C4" s="112"/>
+      <c r="D4" s="112"/>
+      <c r="E4" s="119"/>
+      <c r="F4" s="120"/>
+      <c r="G4" s="120"/>
+      <c r="H4" s="120"/>
+      <c r="I4" s="120"/>
+      <c r="J4" s="120"/>
+      <c r="K4" s="121"/>
+      <c r="L4" s="125" t="s">
         <v>2</v>
       </c>
-      <c r="M4" s="119"/>
-      <c r="N4" s="119"/>
-      <c r="O4" s="120"/>
+      <c r="M4" s="126"/>
+      <c r="N4" s="126"/>
+      <c r="O4" s="127"/>
     </row>
     <row r="5" spans="2:16" s="7" customFormat="1" ht="15" customHeight="1">
       <c r="B5" s="8"/>
@@ -3339,13 +3535,13 @@
       <c r="D8" s="11"/>
       <c r="E8" s="29"/>
       <c r="F8" s="29"/>
-      <c r="G8" s="121" t="s">
-        <v>100</v>
-      </c>
-      <c r="H8" s="121"/>
-      <c r="I8" s="121"/>
-      <c r="J8" s="121"/>
-      <c r="K8" s="121"/>
+      <c r="G8" s="128" t="s">
+        <v>4</v>
+      </c>
+      <c r="H8" s="128"/>
+      <c r="I8" s="128"/>
+      <c r="J8" s="128"/>
+      <c r="K8" s="128"/>
       <c r="L8" s="12"/>
       <c r="M8" s="12"/>
       <c r="N8" s="12"/>
@@ -3518,14 +3714,14 @@
       <c r="O17" s="12"/>
     </row>
     <row r="18" spans="2:24" ht="18" customHeight="1">
-      <c r="B18" s="98" t="s">
-        <v>4</v>
-      </c>
-      <c r="C18" s="98"/>
+      <c r="B18" s="105" t="s">
+        <v>5</v>
+      </c>
+      <c r="C18" s="105"/>
       <c r="D18" s="13"/>
       <c r="E18" s="14"/>
       <c r="F18" s="96" t="s">
-        <v>97</v>
+        <v>6</v>
       </c>
       <c r="G18" s="15"/>
       <c r="H18" s="15"/>
@@ -3548,12 +3744,12 @@
     </row>
     <row r="19" spans="2:24" ht="18" customHeight="1">
       <c r="B19" s="16" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C19" s="16"/>
       <c r="D19" s="17"/>
       <c r="F19" s="97" t="s">
-        <v>98</v>
+        <v>8</v>
       </c>
       <c r="G19" s="19"/>
       <c r="H19" s="19"/>
@@ -3575,10 +3771,10 @@
       <c r="X19" s="12"/>
     </row>
     <row r="20" spans="2:24" ht="18" customHeight="1">
-      <c r="B20" s="99" t="s">
-        <v>6</v>
-      </c>
-      <c r="C20" s="99"/>
+      <c r="B20" s="106" t="s">
+        <v>9</v>
+      </c>
+      <c r="C20" s="106"/>
       <c r="D20" s="17"/>
       <c r="F20" s="18"/>
       <c r="G20" s="19"/>
@@ -3602,12 +3798,12 @@
     </row>
     <row r="21" spans="2:24" ht="18" customHeight="1">
       <c r="B21" s="16" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C21" s="16"/>
       <c r="D21" s="20"/>
       <c r="F21" s="97" t="s">
-        <v>99</v>
+        <v>11</v>
       </c>
       <c r="G21" s="97"/>
       <c r="H21" s="19"/>
@@ -3630,7 +3826,7 @@
     </row>
     <row r="22" spans="2:24" ht="18" customHeight="1">
       <c r="B22" s="21" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C22" s="16"/>
       <c r="D22" s="19"/>
@@ -3656,13 +3852,13 @@
     </row>
     <row r="23" spans="2:24" ht="18" customHeight="1" thickBot="1">
       <c r="B23" s="22" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C23" s="23"/>
       <c r="D23" s="24"/>
       <c r="E23" s="25"/>
       <c r="F23" s="55" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G23" s="24"/>
       <c r="H23" s="24"/>
@@ -3795,18 +3991,18 @@
   <sheetData>
     <row r="1" spans="1:11" ht="25.5">
       <c r="A1" s="2"/>
-      <c r="B1" s="148" t="s">
-        <v>85</v>
-      </c>
-      <c r="C1" s="148"/>
-      <c r="D1" s="148"/>
-      <c r="E1" s="148"/>
-      <c r="F1" s="148"/>
-      <c r="G1" s="148"/>
-      <c r="H1" s="148"/>
-      <c r="I1" s="148"/>
-      <c r="J1" s="148"/>
-      <c r="K1" s="148"/>
+      <c r="B1" s="102" t="s">
+        <v>88</v>
+      </c>
+      <c r="C1" s="102"/>
+      <c r="D1" s="102"/>
+      <c r="E1" s="102"/>
+      <c r="F1" s="102"/>
+      <c r="G1" s="102"/>
+      <c r="H1" s="102"/>
+      <c r="I1" s="102"/>
+      <c r="J1" s="102"/>
+      <c r="K1" s="102"/>
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2"/>
@@ -3824,7 +4020,7 @@
     <row r="3" spans="1:11">
       <c r="A3" s="2"/>
       <c r="B3" s="3" t="s">
-        <v>67</v>
+        <v>38</v>
       </c>
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
@@ -3839,7 +4035,7 @@
     <row r="4" spans="1:11">
       <c r="A4" s="2"/>
       <c r="B4" s="3" t="s">
-        <v>69</v>
+        <v>39</v>
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
@@ -3854,14 +4050,14 @@
     <row r="5" spans="1:11">
       <c r="A5" s="2"/>
       <c r="B5" s="3" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="C5" s="3"/>
       <c r="D5" s="80" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>66</v>
+        <v>41</v>
       </c>
       <c r="F5" s="75"/>
       <c r="G5" s="62"/>
@@ -3886,7 +4082,7 @@
     <row r="7" spans="1:11" ht="15.75">
       <c r="A7" s="2"/>
       <c r="B7" s="73" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="C7" s="74"/>
       <c r="D7" s="74"/>
@@ -3895,7 +4091,7 @@
       <c r="G7" s="74"/>
       <c r="H7" s="74"/>
       <c r="I7" s="74" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="J7" s="74"/>
       <c r="K7" s="74"/>
@@ -3903,13 +4099,13 @@
     <row r="8" spans="1:11" ht="25.5">
       <c r="A8" s="61"/>
       <c r="B8" s="84" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C8" s="85" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="D8" s="85" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="E8" s="60"/>
       <c r="F8" s="60"/>
@@ -3925,7 +4121,7 @@
         <v>1</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="D9" s="1">
         <v>5</v>
@@ -3993,7 +4189,7 @@
     <row r="14" spans="1:11" ht="15.75">
       <c r="A14" s="2"/>
       <c r="B14" s="73" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="C14" s="74"/>
       <c r="D14" s="74"/>
@@ -4008,31 +4204,31 @@
     <row r="15" spans="1:11" ht="38.25">
       <c r="A15" s="2"/>
       <c r="B15" s="86" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C15" s="86" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="D15" s="86" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="E15" s="86" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="F15" s="86" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="G15" s="85" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="H15" s="85" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="I15" s="86" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="J15" s="86" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="K15" s="1"/>
     </row>
@@ -4042,28 +4238,28 @@
         <v>1</v>
       </c>
       <c r="C16" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D16" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="D16" s="2" t="s">
+      <c r="E16" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="F16" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="E16" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>61</v>
-      </c>
       <c r="G16" s="87" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H16" s="2">
         <v>32</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="J16" s="157" t="s">
-        <v>87</v>
+        <v>58</v>
+      </c>
+      <c r="J16" s="162" t="s">
+        <v>91</v>
       </c>
       <c r="K16" s="1"/>
     </row>
@@ -4073,27 +4269,27 @@
         <v>2</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G17" s="83" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H17" s="2">
         <v>32</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="J17" s="157"/>
+        <v>58</v>
+      </c>
+      <c r="J17" s="162"/>
       <c r="K17" s="1"/>
     </row>
     <row r="18" spans="1:11">
@@ -4102,27 +4298,27 @@
         <v>3</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G18" s="87" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H18" s="2">
         <v>32</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="J18" s="157"/>
+        <v>58</v>
+      </c>
+      <c r="J18" s="162"/>
       <c r="K18" s="1"/>
     </row>
     <row r="19" spans="1:11">
@@ -4131,27 +4327,27 @@
         <v>4</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G19" s="81" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H19" s="2">
         <v>32</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="J19" s="157"/>
+        <v>58</v>
+      </c>
+      <c r="J19" s="162"/>
       <c r="K19" s="1"/>
     </row>
     <row r="20" spans="1:11">
@@ -4160,27 +4356,27 @@
         <v>5</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="G20" s="87" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H20" s="2">
         <v>32</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="J20" s="157"/>
+        <v>58</v>
+      </c>
+      <c r="J20" s="162"/>
       <c r="K20" s="1"/>
     </row>
     <row r="21" spans="1:11">
@@ -4193,13 +4389,13 @@
       <c r="G21" s="2"/>
       <c r="H21" s="2"/>
       <c r="I21" s="2"/>
-      <c r="J21" s="157"/>
+      <c r="J21" s="162"/>
       <c r="K21" s="2"/>
     </row>
     <row r="22" spans="1:11" ht="15.75">
       <c r="A22" s="2"/>
       <c r="B22" s="73" t="s">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="C22" s="74"/>
       <c r="D22" s="74"/>
@@ -4214,28 +4410,28 @@
     <row r="23" spans="1:11" ht="25.5">
       <c r="A23" s="28"/>
       <c r="B23" s="85" t="s">
-        <v>12</v>
-      </c>
-      <c r="C23" s="154" t="s">
-        <v>47</v>
-      </c>
-      <c r="D23" s="154"/>
-      <c r="E23" s="154"/>
-      <c r="F23" s="154" t="s">
-        <v>48</v>
-      </c>
-      <c r="G23" s="154"/>
+        <v>16</v>
+      </c>
+      <c r="C23" s="103" t="s">
+        <v>67</v>
+      </c>
+      <c r="D23" s="103"/>
+      <c r="E23" s="103"/>
+      <c r="F23" s="103" t="s">
+        <v>68</v>
+      </c>
+      <c r="G23" s="103"/>
       <c r="H23" s="85" t="s">
-        <v>49</v>
+        <v>69</v>
       </c>
       <c r="I23" s="85" t="s">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="J23" s="85" t="s">
-        <v>51</v>
+        <v>71</v>
       </c>
       <c r="K23" s="85" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -4243,13 +4439,13 @@
       <c r="B24" s="88">
         <v>1</v>
       </c>
-      <c r="C24" s="155" t="s">
-        <v>53</v>
-      </c>
-      <c r="D24" s="155"/>
-      <c r="E24" s="155"/>
-      <c r="F24" s="156"/>
-      <c r="G24" s="156"/>
+      <c r="C24" s="160" t="s">
+        <v>73</v>
+      </c>
+      <c r="D24" s="160"/>
+      <c r="E24" s="160"/>
+      <c r="F24" s="161"/>
+      <c r="G24" s="161"/>
       <c r="H24" s="89"/>
       <c r="I24" s="90"/>
       <c r="J24" s="90"/>
@@ -4291,18 +4487,18 @@
   <sheetData>
     <row r="1" spans="1:11" ht="25.5">
       <c r="A1" s="2"/>
-      <c r="B1" s="148" t="s">
-        <v>89</v>
-      </c>
-      <c r="C1" s="148"/>
-      <c r="D1" s="148"/>
-      <c r="E1" s="148"/>
-      <c r="F1" s="148"/>
-      <c r="G1" s="148"/>
-      <c r="H1" s="148"/>
-      <c r="I1" s="148"/>
-      <c r="J1" s="148"/>
-      <c r="K1" s="148"/>
+      <c r="B1" s="102" t="s">
+        <v>92</v>
+      </c>
+      <c r="C1" s="102"/>
+      <c r="D1" s="102"/>
+      <c r="E1" s="102"/>
+      <c r="F1" s="102"/>
+      <c r="G1" s="102"/>
+      <c r="H1" s="102"/>
+      <c r="I1" s="102"/>
+      <c r="J1" s="102"/>
+      <c r="K1" s="102"/>
     </row>
     <row r="2" spans="1:11" ht="15.75" customHeight="1">
       <c r="A2" s="2"/>
@@ -4320,7 +4516,7 @@
     <row r="3" spans="1:11" ht="15.75" customHeight="1">
       <c r="A3" s="2"/>
       <c r="B3" s="3" t="s">
-        <v>67</v>
+        <v>38</v>
       </c>
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
@@ -4335,7 +4531,7 @@
     <row r="4" spans="1:11">
       <c r="A4" s="2"/>
       <c r="B4" s="3" t="s">
-        <v>69</v>
+        <v>39</v>
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
@@ -4350,14 +4546,14 @@
     <row r="5" spans="1:11" ht="15.75" customHeight="1">
       <c r="A5" s="2"/>
       <c r="B5" s="3" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="C5" s="3"/>
       <c r="D5" s="80" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>66</v>
+        <v>41</v>
       </c>
       <c r="F5" s="75"/>
       <c r="G5" s="62"/>
@@ -4382,7 +4578,7 @@
     <row r="7" spans="1:11" ht="15.75">
       <c r="A7" s="2"/>
       <c r="B7" s="73" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="C7" s="74"/>
       <c r="D7" s="74"/>
@@ -4391,7 +4587,7 @@
       <c r="G7" s="74"/>
       <c r="H7" s="74"/>
       <c r="I7" s="74" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="J7" s="74"/>
       <c r="K7" s="74"/>
@@ -4399,13 +4595,13 @@
     <row r="8" spans="1:11" ht="25.5">
       <c r="A8" s="61"/>
       <c r="B8" s="84" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C8" s="85" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="D8" s="85" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="E8" s="60"/>
       <c r="F8" s="60"/>
@@ -4421,7 +4617,7 @@
         <v>1</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="D9" s="1">
         <v>5</v>
@@ -4489,7 +4685,7 @@
     <row r="14" spans="1:11" ht="15.75">
       <c r="A14" s="2"/>
       <c r="B14" s="73" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="C14" s="74"/>
       <c r="D14" s="74"/>
@@ -4504,31 +4700,31 @@
     <row r="15" spans="1:11" ht="102" customHeight="1">
       <c r="A15" s="2"/>
       <c r="B15" s="86" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C15" s="86" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="D15" s="86" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="E15" s="86" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="F15" s="86" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="G15" s="85" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="H15" s="85" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="I15" s="86" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="J15" s="86" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="K15" s="1"/>
     </row>
@@ -4538,27 +4734,27 @@
         <v>1</v>
       </c>
       <c r="C16" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D16" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="D16" s="2" t="s">
+      <c r="E16" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="F16" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="E16" s="2" t="s">
+      <c r="G16" s="91" t="s">
         <v>75</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="G16" s="91" t="s">
-        <v>71</v>
       </c>
       <c r="H16" s="92">
         <v>40</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="J16" s="157"/>
+        <v>58</v>
+      </c>
+      <c r="J16" s="162"/>
       <c r="K16" s="1"/>
     </row>
     <row r="17" spans="1:11">
@@ -4567,27 +4763,27 @@
         <v>2</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G17" s="93" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="H17" s="92">
         <v>40</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="J17" s="157"/>
+        <v>58</v>
+      </c>
+      <c r="J17" s="162"/>
       <c r="K17" s="1"/>
     </row>
     <row r="18" spans="1:11">
@@ -4596,27 +4792,27 @@
         <v>3</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G18" s="91" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H18" s="92">
         <v>40</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="J18" s="157"/>
+        <v>58</v>
+      </c>
+      <c r="J18" s="162"/>
       <c r="K18" s="1"/>
     </row>
     <row r="19" spans="1:11">
@@ -4625,27 +4821,27 @@
         <v>4</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G19" s="94" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H19" s="92">
         <v>40</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="J19" s="157"/>
+        <v>58</v>
+      </c>
+      <c r="J19" s="162"/>
       <c r="K19" s="1"/>
     </row>
     <row r="20" spans="1:11">
@@ -4654,27 +4850,27 @@
         <v>5</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="G20" s="91" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H20" s="92">
         <v>40</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="J20" s="157"/>
+        <v>58</v>
+      </c>
+      <c r="J20" s="162"/>
       <c r="K20" s="1"/>
     </row>
     <row r="21" spans="1:11">
@@ -4687,13 +4883,13 @@
       <c r="G21" s="2"/>
       <c r="H21" s="2"/>
       <c r="I21" s="2"/>
-      <c r="J21" s="157"/>
+      <c r="J21" s="162"/>
       <c r="K21" s="2"/>
     </row>
     <row r="22" spans="1:11" ht="15.75">
       <c r="A22" s="2"/>
       <c r="B22" s="73" t="s">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="C22" s="74"/>
       <c r="D22" s="74"/>
@@ -4708,43 +4904,43 @@
     <row r="23" spans="1:11" ht="12.75" customHeight="1">
       <c r="A23" s="28"/>
       <c r="B23" s="85" t="s">
-        <v>12</v>
-      </c>
-      <c r="C23" s="154" t="s">
-        <v>47</v>
-      </c>
-      <c r="D23" s="154"/>
-      <c r="E23" s="154"/>
-      <c r="F23" s="154" t="s">
-        <v>48</v>
-      </c>
-      <c r="G23" s="154"/>
+        <v>16</v>
+      </c>
+      <c r="C23" s="103" t="s">
+        <v>67</v>
+      </c>
+      <c r="D23" s="103"/>
+      <c r="E23" s="103"/>
+      <c r="F23" s="103" t="s">
+        <v>68</v>
+      </c>
+      <c r="G23" s="103"/>
       <c r="H23" s="85" t="s">
-        <v>49</v>
+        <v>69</v>
       </c>
       <c r="I23" s="85" t="s">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="J23" s="85" t="s">
-        <v>51</v>
+        <v>71</v>
       </c>
       <c r="K23" s="85" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
     </row>
     <row r="24" spans="1:11">
-      <c r="B24" s="158" t="s">
-        <v>88</v>
-      </c>
-      <c r="C24" s="158"/>
-      <c r="D24" s="158"/>
-      <c r="E24" s="158"/>
-      <c r="F24" s="158"/>
-      <c r="G24" s="158"/>
-      <c r="H24" s="158"/>
-      <c r="I24" s="158"/>
-      <c r="J24" s="158"/>
-      <c r="K24" s="158"/>
+      <c r="B24" s="104" t="s">
+        <v>94</v>
+      </c>
+      <c r="C24" s="104"/>
+      <c r="D24" s="104"/>
+      <c r="E24" s="104"/>
+      <c r="F24" s="104"/>
+      <c r="G24" s="104"/>
+      <c r="H24" s="104"/>
+      <c r="I24" s="104"/>
+      <c r="J24" s="104"/>
+      <c r="K24" s="104"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -4779,18 +4975,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A1" s="148" t="s">
-        <v>91</v>
-      </c>
-      <c r="B1" s="148"/>
-      <c r="C1" s="148"/>
-      <c r="D1" s="148"/>
-      <c r="E1" s="148"/>
-      <c r="F1" s="148"/>
-      <c r="G1" s="148"/>
-      <c r="H1" s="148"/>
-      <c r="I1" s="148"/>
-      <c r="J1" s="148"/>
+      <c r="A1" s="102" t="s">
+        <v>95</v>
+      </c>
+      <c r="B1" s="102"/>
+      <c r="C1" s="102"/>
+      <c r="D1" s="102"/>
+      <c r="E1" s="102"/>
+      <c r="F1" s="102"/>
+      <c r="G1" s="102"/>
+      <c r="H1" s="102"/>
+      <c r="I1" s="102"/>
+      <c r="J1" s="102"/>
     </row>
     <row r="2" spans="1:10" ht="15.75" customHeight="1">
       <c r="A2" s="2"/>
@@ -4806,7 +5002,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="3" t="s">
-        <v>67</v>
+        <v>38</v>
       </c>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
@@ -4820,7 +5016,7 @@
     </row>
     <row r="4" spans="1:10" ht="15.75" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>69</v>
+        <v>39</v>
       </c>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
@@ -4834,14 +5030,14 @@
     </row>
     <row r="5" spans="1:10" ht="15.75" customHeight="1">
       <c r="A5" s="3" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="80" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>66</v>
+        <v>41</v>
       </c>
       <c r="E5" s="75"/>
       <c r="F5" s="62"/>
@@ -4864,7 +5060,7 @@
     </row>
     <row r="7" spans="1:10" ht="15.75">
       <c r="A7" s="73" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="B7" s="74"/>
       <c r="C7" s="74"/>
@@ -4873,20 +5069,20 @@
       <c r="F7" s="74"/>
       <c r="G7" s="74"/>
       <c r="H7" s="74" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="I7" s="74"/>
       <c r="J7" s="74"/>
     </row>
     <row r="8" spans="1:10" ht="15.75" customHeight="1">
       <c r="A8" s="84" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B8" s="85" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="C8" s="85" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="D8" s="60"/>
       <c r="E8" s="60"/>
@@ -4901,7 +5097,7 @@
         <v>1</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="C9" s="1">
         <v>5</v>
@@ -4964,7 +5160,7 @@
     </row>
     <row r="14" spans="1:10" ht="15.75">
       <c r="A14" s="73" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="B14" s="74"/>
       <c r="C14" s="74"/>
@@ -4978,31 +5174,31 @@
     </row>
     <row r="15" spans="1:10" ht="102" customHeight="1">
       <c r="A15" s="86" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B15" s="86" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="C15" s="86" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="D15" s="86" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="E15" s="86" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="F15" s="85" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="G15" s="85" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="H15" s="86" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="I15" s="86" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="J15" s="1"/>
     </row>
@@ -5011,28 +5207,28 @@
         <v>1</v>
       </c>
       <c r="B16" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="D16" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="D16" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>61</v>
-      </c>
       <c r="F16" s="91" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G16" s="92">
         <v>32</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="I16" s="95" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J16" s="1"/>
     </row>
@@ -5041,25 +5237,25 @@
         <v>2</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F17" s="93" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="G17" s="92">
         <v>40</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="I17" s="95"/>
       <c r="J17" s="1"/>
@@ -5069,25 +5265,25 @@
         <v>3</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="D18" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="F18" s="91" t="s">
         <v>75</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="F18" s="91" t="s">
-        <v>71</v>
       </c>
       <c r="G18" s="92">
         <v>40</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="I18" s="95"/>
       <c r="J18" s="1"/>
@@ -5097,25 +5293,25 @@
         <v>4</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F19" s="94" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="G19" s="92">
         <v>40</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="I19" s="95"/>
       <c r="J19" s="1"/>
@@ -5125,25 +5321,25 @@
         <v>5</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="D20" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F20" s="91" t="s">
         <v>75</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="F20" s="91" t="s">
-        <v>71</v>
       </c>
       <c r="G20" s="92">
         <v>40</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="I20" s="95"/>
       <c r="J20" s="1"/>
@@ -5162,7 +5358,7 @@
     </row>
     <row r="22" spans="1:10" ht="15.75">
       <c r="A22" s="73" t="s">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="B22" s="74"/>
       <c r="C22" s="74"/>
@@ -5176,43 +5372,43 @@
     </row>
     <row r="23" spans="1:10" ht="12.75" customHeight="1">
       <c r="A23" s="85" t="s">
-        <v>12</v>
-      </c>
-      <c r="B23" s="154" t="s">
-        <v>47</v>
-      </c>
-      <c r="C23" s="154"/>
-      <c r="D23" s="154"/>
-      <c r="E23" s="154" t="s">
-        <v>48</v>
-      </c>
-      <c r="F23" s="154"/>
+        <v>16</v>
+      </c>
+      <c r="B23" s="103" t="s">
+        <v>67</v>
+      </c>
+      <c r="C23" s="103"/>
+      <c r="D23" s="103"/>
+      <c r="E23" s="103" t="s">
+        <v>68</v>
+      </c>
+      <c r="F23" s="103"/>
       <c r="G23" s="85" t="s">
-        <v>49</v>
+        <v>69</v>
       </c>
       <c r="H23" s="85" t="s">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="I23" s="85" t="s">
-        <v>51</v>
+        <v>71</v>
       </c>
       <c r="J23" s="85" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
     </row>
     <row r="24" spans="1:10">
-      <c r="A24" s="158" t="s">
-        <v>88</v>
-      </c>
-      <c r="B24" s="158"/>
-      <c r="C24" s="158"/>
-      <c r="D24" s="158"/>
-      <c r="E24" s="158"/>
-      <c r="F24" s="158"/>
-      <c r="G24" s="158"/>
-      <c r="H24" s="158"/>
-      <c r="I24" s="158"/>
-      <c r="J24" s="158"/>
+      <c r="A24" s="104" t="s">
+        <v>94</v>
+      </c>
+      <c r="B24" s="104"/>
+      <c r="C24" s="104"/>
+      <c r="D24" s="104"/>
+      <c r="E24" s="104"/>
+      <c r="F24" s="104"/>
+      <c r="G24" s="104"/>
+      <c r="H24" s="104"/>
+      <c r="I24" s="104"/>
+      <c r="J24" s="104"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -5246,18 +5442,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A1" s="148" t="s">
-        <v>94</v>
-      </c>
-      <c r="B1" s="148"/>
-      <c r="C1" s="148"/>
-      <c r="D1" s="148"/>
-      <c r="E1" s="148"/>
-      <c r="F1" s="148"/>
-      <c r="G1" s="148"/>
-      <c r="H1" s="148"/>
-      <c r="I1" s="148"/>
-      <c r="J1" s="148"/>
+      <c r="A1" s="102" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1" s="102"/>
+      <c r="C1" s="102"/>
+      <c r="D1" s="102"/>
+      <c r="E1" s="102"/>
+      <c r="F1" s="102"/>
+      <c r="G1" s="102"/>
+      <c r="H1" s="102"/>
+      <c r="I1" s="102"/>
+      <c r="J1" s="102"/>
     </row>
     <row r="2" spans="1:10" ht="15.75" customHeight="1">
       <c r="A2" s="2"/>
@@ -5273,7 +5469,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="3" t="s">
-        <v>67</v>
+        <v>38</v>
       </c>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
@@ -5287,7 +5483,7 @@
     </row>
     <row r="4" spans="1:10" ht="15.75" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>69</v>
+        <v>39</v>
       </c>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
@@ -5301,14 +5497,14 @@
     </row>
     <row r="5" spans="1:10" ht="15.75" customHeight="1">
       <c r="A5" s="3" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="80">
         <v>46210</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>66</v>
+        <v>41</v>
       </c>
       <c r="E5" s="75"/>
       <c r="F5" s="62"/>
@@ -5331,7 +5527,7 @@
     </row>
     <row r="7" spans="1:10" ht="15.75">
       <c r="A7" s="73" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="B7" s="74"/>
       <c r="C7" s="74"/>
@@ -5340,20 +5536,20 @@
       <c r="F7" s="74"/>
       <c r="G7" s="74"/>
       <c r="H7" s="74" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="I7" s="74"/>
       <c r="J7" s="74"/>
     </row>
     <row r="8" spans="1:10" ht="15.75" customHeight="1">
       <c r="A8" s="84" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B8" s="85" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="C8" s="85" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="D8" s="60"/>
       <c r="E8" s="60"/>
@@ -5368,7 +5564,7 @@
         <v>1</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="C9" s="1">
         <v>5</v>
@@ -5431,7 +5627,7 @@
     </row>
     <row r="14" spans="1:10" ht="15.75">
       <c r="A14" s="73" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="B14" s="74"/>
       <c r="C14" s="74"/>
@@ -5445,31 +5641,31 @@
     </row>
     <row r="15" spans="1:10" ht="102" customHeight="1">
       <c r="A15" s="86" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B15" s="86" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="C15" s="86" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="D15" s="86" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="E15" s="86" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="F15" s="85" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="G15" s="85" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="H15" s="86" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="I15" s="86" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="J15" s="1"/>
     </row>
@@ -5478,28 +5674,28 @@
         <v>1</v>
       </c>
       <c r="B16" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="D16" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="D16" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>61</v>
-      </c>
       <c r="F16" s="91" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G16" s="92">
         <v>36</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="I16" s="95" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="J16" s="1"/>
     </row>
@@ -5508,25 +5704,25 @@
         <v>2</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F17" s="93" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="G17" s="92">
         <v>40</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="I17" s="95"/>
       <c r="J17" s="1"/>
@@ -5536,28 +5732,28 @@
         <v>3</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="D18" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="F18" s="91" t="s">
         <v>75</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="F18" s="91" t="s">
-        <v>71</v>
       </c>
       <c r="G18" s="92">
         <v>32</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="I18" s="95" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="J18" s="1"/>
     </row>
@@ -5566,28 +5762,28 @@
         <v>4</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F19" s="94" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="G19" s="92">
         <v>36</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="I19" s="95" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="J19" s="1"/>
     </row>
@@ -5596,25 +5792,25 @@
         <v>5</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="D20" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F20" s="91" t="s">
         <v>75</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="F20" s="91" t="s">
-        <v>71</v>
       </c>
       <c r="G20" s="92">
         <v>40</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="I20" s="95"/>
       <c r="J20" s="1"/>
@@ -5633,7 +5829,7 @@
     </row>
     <row r="22" spans="1:10" ht="15.75">
       <c r="A22" s="73" t="s">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="B22" s="74"/>
       <c r="C22" s="74"/>
@@ -5647,43 +5843,43 @@
     </row>
     <row r="23" spans="1:10" ht="12.75" customHeight="1">
       <c r="A23" s="85" t="s">
-        <v>12</v>
-      </c>
-      <c r="B23" s="154" t="s">
-        <v>47</v>
-      </c>
-      <c r="C23" s="154"/>
-      <c r="D23" s="154"/>
-      <c r="E23" s="154" t="s">
-        <v>48</v>
-      </c>
-      <c r="F23" s="154"/>
+        <v>16</v>
+      </c>
+      <c r="B23" s="103" t="s">
+        <v>67</v>
+      </c>
+      <c r="C23" s="103"/>
+      <c r="D23" s="103"/>
+      <c r="E23" s="103" t="s">
+        <v>68</v>
+      </c>
+      <c r="F23" s="103"/>
       <c r="G23" s="85" t="s">
-        <v>49</v>
+        <v>69</v>
       </c>
       <c r="H23" s="85" t="s">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="I23" s="85" t="s">
-        <v>51</v>
+        <v>71</v>
       </c>
       <c r="J23" s="85" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
     </row>
     <row r="24" spans="1:10">
-      <c r="A24" s="158" t="s">
-        <v>88</v>
-      </c>
-      <c r="B24" s="158"/>
-      <c r="C24" s="158"/>
-      <c r="D24" s="158"/>
-      <c r="E24" s="158"/>
-      <c r="F24" s="158"/>
-      <c r="G24" s="158"/>
-      <c r="H24" s="158"/>
-      <c r="I24" s="158"/>
-      <c r="J24" s="158"/>
+      <c r="A24" s="104" t="s">
+        <v>94</v>
+      </c>
+      <c r="B24" s="104"/>
+      <c r="C24" s="104"/>
+      <c r="D24" s="104"/>
+      <c r="E24" s="104"/>
+      <c r="F24" s="104"/>
+      <c r="G24" s="104"/>
+      <c r="H24" s="104"/>
+      <c r="I24" s="104"/>
+      <c r="J24" s="104"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -5699,467 +5895,723 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E10C33C4-097E-4EEE-9C6E-F53E06C2B87A}">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:J24"/>
-  <sheetFormatPr defaultRowHeight="12.75"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9900BC41-8DB7-45A5-8AAA-EB2309208EF3}">
+  <dimension ref="A1:AK32"/>
+  <sheetFormatPr defaultColWidth="3.42578125" defaultRowHeight="15.6" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="3.140625" customWidth="1"/>
-    <col min="2" max="4" width="18" customWidth="1"/>
-    <col min="5" max="5" width="11.42578125" customWidth="1"/>
-    <col min="6" max="6" width="24.85546875" customWidth="1"/>
-    <col min="7" max="7" width="20.42578125" customWidth="1"/>
-    <col min="8" max="8" width="19.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="53.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="27.5703125" customWidth="1"/>
+    <col min="1" max="1" width="1.5703125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="3.140625" style="2" customWidth="1"/>
+    <col min="3" max="5" width="18" style="2" customWidth="1"/>
+    <col min="6" max="6" width="24.7109375" style="75" customWidth="1"/>
+    <col min="7" max="7" width="17.28515625" style="2" customWidth="1"/>
+    <col min="8" max="8" width="21" style="2" customWidth="1"/>
+    <col min="9" max="9" width="26.42578125" style="2" customWidth="1"/>
+    <col min="10" max="10" width="25.7109375" style="2" customWidth="1"/>
+    <col min="11" max="11" width="27.5703125" style="2" customWidth="1"/>
+    <col min="12" max="14" width="3.7109375" style="2" customWidth="1"/>
+    <col min="15" max="20" width="3.140625" style="2" customWidth="1"/>
+    <col min="21" max="33" width="3.5703125" style="2" customWidth="1"/>
+    <col min="34" max="16384" width="3.42578125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A1" s="148" t="s">
+    <row r="1" spans="2:37" ht="25.5">
+      <c r="B1" s="102" t="s">
         <v>101</v>
       </c>
-      <c r="B1" s="148"/>
-      <c r="C1" s="148"/>
-      <c r="D1" s="148"/>
-      <c r="E1" s="148"/>
-      <c r="F1" s="148"/>
-      <c r="G1" s="148"/>
-      <c r="H1" s="148"/>
-      <c r="I1" s="148"/>
-      <c r="J1" s="148"/>
-    </row>
-    <row r="2" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A2" s="2"/>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="75"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
-    </row>
-    <row r="3" spans="1:10">
-      <c r="A3" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="B3" s="3"/>
+      <c r="C1" s="102"/>
+      <c r="D1" s="102"/>
+      <c r="E1" s="102"/>
+      <c r="F1" s="102"/>
+      <c r="G1" s="102"/>
+      <c r="H1" s="102"/>
+      <c r="I1" s="102"/>
+      <c r="J1" s="102"/>
+      <c r="K1" s="102"/>
+      <c r="L1" s="63"/>
+      <c r="M1" s="63"/>
+      <c r="N1" s="63"/>
+      <c r="O1" s="63"/>
+      <c r="P1" s="63"/>
+      <c r="Q1" s="63"/>
+      <c r="R1" s="63"/>
+      <c r="S1" s="63"/>
+      <c r="T1" s="63"/>
+      <c r="U1" s="63"/>
+      <c r="V1" s="63"/>
+      <c r="W1" s="63"/>
+      <c r="X1" s="63"/>
+      <c r="Y1" s="63"/>
+      <c r="Z1" s="63"/>
+      <c r="AA1" s="63"/>
+      <c r="AB1" s="63"/>
+      <c r="AC1" s="63"/>
+      <c r="AD1" s="63"/>
+      <c r="AE1" s="63"/>
+      <c r="AF1" s="63"/>
+      <c r="AG1" s="63"/>
+    </row>
+    <row r="3" spans="2:37" ht="15.6" customHeight="1">
+      <c r="B3" s="3" t="s">
+        <v>38</v>
+      </c>
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
-      <c r="E3" s="75"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2"/>
-      <c r="I3" s="2"/>
-      <c r="J3" s="2"/>
-    </row>
-    <row r="4" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A4" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="B4" s="3"/>
+      <c r="E3" s="3"/>
+    </row>
+    <row r="4" spans="2:37" ht="15.6" customHeight="1">
+      <c r="B4" s="3" t="s">
+        <v>39</v>
+      </c>
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
-      <c r="E4" s="75"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2"/>
-    </row>
-    <row r="5" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A5" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="B5" s="3"/>
-      <c r="C5" s="80" t="s">
+      <c r="E4" s="3"/>
+    </row>
+    <row r="5" spans="2:37" ht="15.6" customHeight="1">
+      <c r="B5" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C5" s="3"/>
+      <c r="D5" s="98" t="s">
         <v>102</v>
       </c>
-      <c r="D5" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="E5" s="75"/>
-      <c r="F5" s="62"/>
+      <c r="E5" s="3" t="s">
+        <v>41</v>
+      </c>
       <c r="G5" s="62"/>
       <c r="H5" s="62"/>
       <c r="I5" s="62"/>
       <c r="J5" s="62"/>
-    </row>
-    <row r="6" spans="1:10">
-      <c r="A6" s="1"/>
+      <c r="K5" s="62"/>
+      <c r="L5" s="64"/>
+      <c r="M5" s="64"/>
+    </row>
+    <row r="6" spans="2:37" ht="15.6" customHeight="1">
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
-      <c r="E6" s="76"/>
-      <c r="F6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="76"/>
       <c r="G6" s="1"/>
       <c r="H6" s="1"/>
       <c r="I6" s="1"/>
       <c r="J6" s="1"/>
-    </row>
-    <row r="7" spans="1:10" ht="15.75">
-      <c r="A7" s="73" t="s">
-        <v>34</v>
-      </c>
-      <c r="B7" s="74"/>
+      <c r="K6" s="1"/>
+    </row>
+    <row r="7" spans="2:37" ht="15.75">
+      <c r="B7" s="73" t="s">
+        <v>103</v>
+      </c>
       <c r="C7" s="74"/>
       <c r="D7" s="74"/>
       <c r="E7" s="74"/>
       <c r="F7" s="74"/>
       <c r="G7" s="74"/>
-      <c r="H7" s="74" t="s">
-        <v>35</v>
-      </c>
-      <c r="I7" s="74"/>
+      <c r="H7" s="74"/>
+      <c r="I7" s="74" t="s">
+        <v>43</v>
+      </c>
       <c r="J7" s="74"/>
-    </row>
-    <row r="8" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A8" s="84" t="s">
-        <v>12</v>
-      </c>
-      <c r="B8" s="85" t="s">
-        <v>36</v>
-      </c>
-      <c r="C8" s="85" t="s">
-        <v>37</v>
-      </c>
-      <c r="D8" s="60"/>
-      <c r="E8" s="60"/>
-      <c r="F8" s="60"/>
-      <c r="G8" s="60"/>
-      <c r="H8" s="60"/>
-      <c r="I8" s="60"/>
-      <c r="J8" s="60"/>
-    </row>
-    <row r="9" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A9" s="1">
-        <v>1</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="C9" s="1">
-        <v>5</v>
-      </c>
-      <c r="D9" s="60"/>
-      <c r="E9" s="60"/>
-      <c r="F9" s="60"/>
-      <c r="G9" s="1"/>
-      <c r="H9" s="1"/>
-      <c r="I9" s="1"/>
-      <c r="J9" s="1"/>
-    </row>
-    <row r="10" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A10" s="60"/>
-      <c r="B10" s="60"/>
-      <c r="C10" s="60"/>
+      <c r="K7" s="74"/>
+      <c r="L7" s="65"/>
+      <c r="M7" s="65"/>
+      <c r="N7" s="65"/>
+      <c r="O7" s="65"/>
+      <c r="P7" s="65"/>
+      <c r="Q7" s="65"/>
+      <c r="R7" s="65"/>
+      <c r="S7" s="65"/>
+      <c r="T7" s="65"/>
+      <c r="U7" s="65"/>
+      <c r="V7" s="65"/>
+      <c r="W7" s="65"/>
+      <c r="X7" s="65"/>
+      <c r="Y7" s="65"/>
+      <c r="Z7" s="65"/>
+      <c r="AA7" s="65"/>
+      <c r="AB7" s="65"/>
+      <c r="AC7" s="65"/>
+      <c r="AD7" s="65"/>
+      <c r="AE7" s="65"/>
+      <c r="AF7" s="65"/>
+      <c r="AG7" s="65"/>
+      <c r="AH7" s="65"/>
+      <c r="AI7" s="65"/>
+      <c r="AJ7" s="65"/>
+      <c r="AK7" s="65"/>
+    </row>
+    <row r="8" spans="2:37" s="61" customFormat="1" ht="25.5">
+      <c r="B8" s="72" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" s="77" t="s">
+        <v>44</v>
+      </c>
+      <c r="D8" s="69" t="s">
+        <v>104</v>
+      </c>
+      <c r="E8" s="69" t="s">
+        <v>105</v>
+      </c>
+      <c r="F8" s="69" t="s">
+        <v>106</v>
+      </c>
+      <c r="G8" s="69" t="s">
+        <v>107</v>
+      </c>
+      <c r="H8" s="163" t="s">
+        <v>90</v>
+      </c>
+      <c r="I8" s="163"/>
+      <c r="J8" s="163"/>
+      <c r="K8" s="163"/>
+    </row>
+    <row r="9" spans="2:37" ht="12.75">
+      <c r="B9" s="168" t="s">
+        <v>73</v>
+      </c>
+      <c r="C9" s="169"/>
+      <c r="D9" s="170"/>
+      <c r="E9" s="171"/>
+      <c r="F9" s="171"/>
+      <c r="G9" s="171"/>
+      <c r="H9" s="172"/>
+      <c r="I9" s="172"/>
+      <c r="J9" s="172"/>
+      <c r="K9" s="172"/>
+    </row>
+    <row r="10" spans="2:37" ht="15.6" customHeight="1">
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
       <c r="D10" s="1"/>
       <c r="E10" s="1"/>
-      <c r="F10" s="1"/>
+      <c r="F10" s="76"/>
       <c r="G10" s="1"/>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
-      <c r="J10" s="2"/>
-    </row>
-    <row r="11" spans="1:10">
-      <c r="A11" s="60"/>
-      <c r="B11" s="60"/>
-      <c r="C11" s="60"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
-      <c r="F11" s="1"/>
-      <c r="G11" s="1"/>
-      <c r="H11" s="2"/>
-      <c r="I11" s="2"/>
-      <c r="J11" s="2"/>
-    </row>
-    <row r="12" spans="1:10">
-      <c r="A12" s="60"/>
-      <c r="B12" s="60"/>
-      <c r="C12" s="60"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="1"/>
-      <c r="F12" s="1"/>
-      <c r="G12" s="1"/>
-      <c r="H12" s="2"/>
-      <c r="I12" s="2"/>
-      <c r="J12" s="2"/>
-    </row>
-    <row r="13" spans="1:10">
-      <c r="A13" s="1"/>
-      <c r="B13" s="1"/>
-      <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
-      <c r="E13" s="76"/>
-      <c r="F13" s="1"/>
-      <c r="G13" s="1"/>
-      <c r="H13" s="1"/>
-      <c r="I13" s="1"/>
-      <c r="J13" s="1"/>
-    </row>
-    <row r="14" spans="1:10" ht="15.75">
-      <c r="A14" s="73" t="s">
-        <v>38</v>
-      </c>
-      <c r="B14" s="74"/>
-      <c r="C14" s="74"/>
-      <c r="D14" s="74"/>
-      <c r="E14" s="74"/>
-      <c r="F14" s="74"/>
-      <c r="G14" s="74"/>
-      <c r="H14" s="74"/>
-      <c r="I14" s="1"/>
-      <c r="J14" s="1"/>
-    </row>
-    <row r="15" spans="1:10" ht="102" customHeight="1">
-      <c r="A15" s="86" t="s">
-        <v>12</v>
-      </c>
-      <c r="B15" s="86" t="s">
-        <v>39</v>
-      </c>
-      <c r="C15" s="86" t="s">
+      <c r="H10" s="1"/>
+      <c r="I10" s="1"/>
+      <c r="J10" s="1"/>
+      <c r="K10" s="1"/>
+    </row>
+    <row r="11" spans="2:37" ht="15.75">
+      <c r="B11" s="73" t="s">
+        <v>108</v>
+      </c>
+      <c r="C11" s="74"/>
+      <c r="D11" s="74"/>
+      <c r="E11" s="74"/>
+      <c r="F11" s="74"/>
+      <c r="G11" s="74"/>
+      <c r="H11" s="74"/>
+      <c r="I11" s="74" t="s">
+        <v>43</v>
+      </c>
+      <c r="J11" s="74"/>
+      <c r="K11" s="74"/>
+    </row>
+    <row r="12" spans="2:37" ht="12.75">
+      <c r="B12" s="71" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" s="71" t="s">
+        <v>44</v>
+      </c>
+      <c r="D12" s="71" t="s">
+        <v>109</v>
+      </c>
+      <c r="E12" s="71" t="s">
+        <v>110</v>
+      </c>
+      <c r="F12" s="77" t="s">
+        <v>111</v>
+      </c>
+      <c r="G12" s="163" t="s">
+        <v>90</v>
+      </c>
+      <c r="H12" s="163"/>
+      <c r="I12" s="163"/>
+      <c r="J12" s="163"/>
+      <c r="K12" s="163"/>
+    </row>
+    <row r="13" spans="2:37" ht="12.75">
+      <c r="B13" s="58">
+        <v>1</v>
+      </c>
+      <c r="C13" s="59" t="s">
+        <v>46</v>
+      </c>
+      <c r="D13" s="58" t="s">
+        <v>55</v>
+      </c>
+      <c r="E13" s="58" t="s">
+        <v>81</v>
+      </c>
+      <c r="F13" s="78" t="s">
+        <v>112</v>
+      </c>
+      <c r="G13" s="58"/>
+      <c r="H13" s="58"/>
+      <c r="I13" s="58"/>
+      <c r="J13" s="58"/>
+      <c r="K13" s="58"/>
+    </row>
+    <row r="14" spans="2:37" ht="12.75">
+      <c r="B14" s="58">
+        <v>2</v>
+      </c>
+      <c r="C14" s="59" t="s">
+        <v>46</v>
+      </c>
+      <c r="D14" s="58" t="s">
+        <v>59</v>
+      </c>
+      <c r="E14" s="58" t="s">
+        <v>82</v>
+      </c>
+      <c r="F14" s="78" t="s">
+        <v>112</v>
+      </c>
+      <c r="G14" s="99"/>
+      <c r="H14" s="99"/>
+      <c r="I14" s="99"/>
+      <c r="J14" s="99"/>
+      <c r="K14" s="99"/>
+    </row>
+    <row r="15" spans="2:37" ht="12.75">
+      <c r="B15" s="58">
+        <v>3</v>
+      </c>
+      <c r="C15" s="59" t="s">
+        <v>46</v>
+      </c>
+      <c r="D15" s="58" t="s">
+        <v>62</v>
+      </c>
+      <c r="E15" s="58" t="s">
+        <v>81</v>
+      </c>
+      <c r="F15" s="78" t="s">
+        <v>112</v>
+      </c>
+      <c r="G15" s="99"/>
+      <c r="H15" s="99"/>
+      <c r="I15" s="99"/>
+      <c r="J15" s="99"/>
+      <c r="K15" s="99"/>
+    </row>
+    <row r="16" spans="2:37" ht="12.75">
+      <c r="B16" s="58">
+        <v>4</v>
+      </c>
+      <c r="C16" s="59" t="s">
+        <v>46</v>
+      </c>
+      <c r="D16" s="58" t="s">
+        <v>63</v>
+      </c>
+      <c r="E16" s="58" t="s">
+        <v>82</v>
+      </c>
+      <c r="F16" s="78" t="s">
+        <v>112</v>
+      </c>
+      <c r="G16" s="99"/>
+      <c r="H16" s="99"/>
+      <c r="I16" s="99"/>
+      <c r="J16" s="99"/>
+      <c r="K16" s="99"/>
+    </row>
+    <row r="17" spans="1:37" ht="15.75">
+      <c r="B17" s="58">
+        <v>5</v>
+      </c>
+      <c r="C17" s="59" t="s">
+        <v>46</v>
+      </c>
+      <c r="D17" s="58" t="s">
+        <v>64</v>
+      </c>
+      <c r="E17" s="58" t="s">
+        <v>81</v>
+      </c>
+      <c r="F17" s="78" t="s">
+        <v>112</v>
+      </c>
+      <c r="G17" s="164"/>
+      <c r="H17" s="164"/>
+      <c r="I17" s="164"/>
+      <c r="J17" s="164"/>
+      <c r="K17" s="164"/>
+      <c r="L17" s="66"/>
+      <c r="M17" s="66"/>
+      <c r="N17" s="66"/>
+      <c r="O17" s="66"/>
+      <c r="P17" s="66"/>
+      <c r="Q17" s="66"/>
+      <c r="R17" s="66"/>
+      <c r="S17" s="66"/>
+      <c r="T17" s="66"/>
+      <c r="U17" s="66"/>
+      <c r="V17" s="66"/>
+      <c r="W17" s="66"/>
+      <c r="X17" s="66"/>
+      <c r="Y17" s="66"/>
+      <c r="Z17" s="66"/>
+      <c r="AA17" s="66"/>
+      <c r="AB17" s="66"/>
+      <c r="AC17" s="66"/>
+      <c r="AD17" s="66"/>
+      <c r="AE17" s="66"/>
+      <c r="AF17" s="66"/>
+      <c r="AG17" s="66"/>
+      <c r="AH17" s="66"/>
+      <c r="AI17" s="66"/>
+      <c r="AJ17" s="66"/>
+      <c r="AK17" s="66"/>
+    </row>
+    <row r="18" spans="1:37" ht="35.1" customHeight="1">
+      <c r="L18" s="1"/>
+      <c r="M18" s="1"/>
+      <c r="N18" s="1"/>
+    </row>
+    <row r="19" spans="1:37" ht="15.75">
+      <c r="B19" s="73" t="s">
+        <v>113</v>
+      </c>
+      <c r="C19" s="74"/>
+      <c r="D19" s="74"/>
+      <c r="E19" s="74"/>
+      <c r="F19" s="74"/>
+      <c r="G19" s="74"/>
+      <c r="H19" s="74"/>
+      <c r="I19" s="74"/>
+      <c r="J19" s="74"/>
+      <c r="K19" s="74"/>
+    </row>
+    <row r="20" spans="1:37" ht="38.25">
+      <c r="B20" s="71" t="s">
+        <v>16</v>
+      </c>
+      <c r="C20" s="100" t="s">
+        <v>48</v>
+      </c>
+      <c r="D20" s="100" t="s">
+        <v>49</v>
+      </c>
+      <c r="E20" s="100" t="s">
+        <v>44</v>
+      </c>
+      <c r="F20" s="77" t="s">
+        <v>50</v>
+      </c>
+      <c r="G20" s="69" t="s">
+        <v>114</v>
+      </c>
+      <c r="H20" s="69" t="s">
+        <v>115</v>
+      </c>
+      <c r="I20" s="69" t="s">
+        <v>116</v>
+      </c>
+      <c r="J20" s="71" t="s">
+        <v>52</v>
+      </c>
+      <c r="K20" s="71" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="21" spans="1:37" ht="15.6" customHeight="1">
+      <c r="B21" s="58">
+        <v>1</v>
+      </c>
+      <c r="C21" s="58" t="s">
+        <v>54</v>
+      </c>
+      <c r="D21" s="58" t="s">
+        <v>55</v>
+      </c>
+      <c r="E21" s="58" t="s">
+        <v>56</v>
+      </c>
+      <c r="F21" s="101" t="s">
+        <v>57</v>
+      </c>
+      <c r="G21" s="99">
+        <v>0</v>
+      </c>
+      <c r="H21" s="99">
         <v>40</v>
       </c>
-      <c r="D15" s="86" t="s">
-        <v>74</v>
-      </c>
-      <c r="E15" s="86" t="s">
-        <v>36</v>
-      </c>
-      <c r="F15" s="85" t="s">
-        <v>41</v>
-      </c>
-      <c r="G15" s="85" t="s">
-        <v>42</v>
-      </c>
-      <c r="H15" s="86" t="s">
-        <v>43</v>
-      </c>
-      <c r="I15" s="86" t="s">
-        <v>86</v>
-      </c>
-      <c r="J15" s="1"/>
-    </row>
-    <row r="16" spans="1:10">
-      <c r="A16" s="2">
-        <v>1</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="C16" s="2" t="s">
+      <c r="I21" s="99">
+        <v>0</v>
+      </c>
+      <c r="J21" s="165" t="s">
+        <v>58</v>
+      </c>
+      <c r="K21" s="165" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="22" spans="1:37" ht="15.75">
+      <c r="B22" s="58">
+        <v>2</v>
+      </c>
+      <c r="C22" s="58" t="s">
+        <v>54</v>
+      </c>
+      <c r="D22" s="58" t="s">
+        <v>59</v>
+      </c>
+      <c r="E22" s="58" t="s">
+        <v>60</v>
+      </c>
+      <c r="F22" s="101" t="s">
+        <v>57</v>
+      </c>
+      <c r="G22" s="99">
+        <v>0</v>
+      </c>
+      <c r="H22" s="99">
+        <v>40</v>
+      </c>
+      <c r="I22" s="99">
+        <v>0</v>
+      </c>
+      <c r="J22" s="166"/>
+      <c r="K22" s="166"/>
+      <c r="L22" s="66"/>
+      <c r="M22" s="66"/>
+      <c r="N22" s="66"/>
+      <c r="O22" s="66"/>
+      <c r="P22" s="66"/>
+      <c r="Q22" s="66"/>
+      <c r="R22" s="66"/>
+      <c r="S22" s="66"/>
+      <c r="T22" s="66"/>
+      <c r="U22" s="66"/>
+      <c r="V22" s="66"/>
+      <c r="W22" s="66"/>
+      <c r="X22" s="66"/>
+      <c r="Y22" s="66"/>
+      <c r="Z22" s="66"/>
+      <c r="AA22" s="66"/>
+      <c r="AB22" s="66"/>
+      <c r="AC22" s="66"/>
+      <c r="AD22" s="66"/>
+      <c r="AE22" s="66"/>
+      <c r="AF22" s="66"/>
+      <c r="AG22" s="66"/>
+      <c r="AH22" s="66"/>
+      <c r="AI22" s="66"/>
+      <c r="AJ22" s="66"/>
+      <c r="AK22" s="66"/>
+    </row>
+    <row r="23" spans="1:37" ht="12.75">
+      <c r="B23" s="58">
+        <v>3</v>
+      </c>
+      <c r="C23" s="58" t="s">
+        <v>54</v>
+      </c>
+      <c r="D23" s="58" t="s">
+        <v>62</v>
+      </c>
+      <c r="E23" s="58" t="s">
+        <v>60</v>
+      </c>
+      <c r="F23" s="101" t="s">
+        <v>57</v>
+      </c>
+      <c r="G23" s="99">
+        <v>0</v>
+      </c>
+      <c r="H23" s="99">
+        <v>40</v>
+      </c>
+      <c r="I23" s="99">
+        <v>0</v>
+      </c>
+      <c r="J23" s="166"/>
+      <c r="K23" s="166"/>
+    </row>
+    <row r="24" spans="1:37" ht="15.6" customHeight="1">
+      <c r="B24" s="58">
+        <v>4</v>
+      </c>
+      <c r="C24" s="58" t="s">
+        <v>54</v>
+      </c>
+      <c r="D24" s="58" t="s">
+        <v>63</v>
+      </c>
+      <c r="E24" s="58" t="s">
+        <v>60</v>
+      </c>
+      <c r="F24" s="101" t="s">
+        <v>57</v>
+      </c>
+      <c r="G24" s="99">
+        <v>0</v>
+      </c>
+      <c r="H24" s="99">
+        <v>40</v>
+      </c>
+      <c r="I24" s="99">
+        <v>0</v>
+      </c>
+      <c r="J24" s="166"/>
+      <c r="K24" s="166"/>
+    </row>
+    <row r="25" spans="1:37" ht="15.6" customHeight="1">
+      <c r="B25" s="58">
+        <v>5</v>
+      </c>
+      <c r="C25" s="58" t="s">
+        <v>54</v>
+      </c>
+      <c r="D25" s="58" t="s">
+        <v>64</v>
+      </c>
+      <c r="E25" s="58" t="s">
         <v>56</v>
       </c>
-      <c r="D16" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="F16" s="91" t="s">
-        <v>63</v>
-      </c>
-      <c r="G16" s="92">
+      <c r="F25" s="101" t="s">
+        <v>57</v>
+      </c>
+      <c r="G25" s="99">
+        <v>0</v>
+      </c>
+      <c r="H25" s="99">
         <v>40</v>
       </c>
-      <c r="H16" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="I16" s="95"/>
-      <c r="J16" s="1"/>
-    </row>
-    <row r="17" spans="1:10">
-      <c r="A17" s="2">
-        <v>2</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="F17" s="91" t="s">
-        <v>63</v>
-      </c>
-      <c r="G17" s="92">
-        <v>40</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="I17" s="95"/>
-      <c r="J17" s="1"/>
-    </row>
-    <row r="18" spans="1:10">
-      <c r="A18" s="2">
-        <v>3</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="F18" s="91" t="s">
-        <v>63</v>
-      </c>
-      <c r="G18" s="92">
-        <v>40</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="I18" s="95"/>
-      <c r="J18" s="1"/>
-    </row>
-    <row r="19" spans="1:10">
-      <c r="A19" s="2">
-        <v>4</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="F19" s="91" t="s">
-        <v>63</v>
-      </c>
-      <c r="G19" s="92">
-        <v>40</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="I19" s="95"/>
-      <c r="J19" s="1"/>
-    </row>
-    <row r="20" spans="1:10">
-      <c r="A20" s="2">
-        <v>5</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="F20" s="91" t="s">
-        <v>63</v>
-      </c>
-      <c r="G20" s="92">
-        <v>40</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="I20" s="95"/>
-      <c r="J20" s="1"/>
-    </row>
-    <row r="21" spans="1:10">
-      <c r="A21" s="2"/>
-      <c r="B21" s="2"/>
-      <c r="C21" s="2"/>
-      <c r="D21" s="2"/>
-      <c r="E21" s="75"/>
-      <c r="F21" s="2"/>
-      <c r="G21" s="2"/>
-      <c r="H21" s="2"/>
-      <c r="I21" s="95"/>
-      <c r="J21" s="2"/>
-    </row>
-    <row r="22" spans="1:10" ht="15.75">
-      <c r="A22" s="73" t="s">
-        <v>46</v>
-      </c>
-      <c r="B22" s="74"/>
-      <c r="C22" s="74"/>
-      <c r="D22" s="74"/>
-      <c r="E22" s="74"/>
-      <c r="F22" s="74"/>
-      <c r="G22" s="74"/>
-      <c r="H22" s="74"/>
-      <c r="I22" s="74"/>
-      <c r="J22" s="74"/>
-    </row>
-    <row r="23" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A23" s="85" t="s">
-        <v>12</v>
-      </c>
-      <c r="B23" s="154" t="s">
-        <v>47</v>
-      </c>
-      <c r="C23" s="154"/>
-      <c r="D23" s="154"/>
-      <c r="E23" s="154" t="s">
-        <v>48</v>
-      </c>
-      <c r="F23" s="154"/>
-      <c r="G23" s="85" t="s">
-        <v>49</v>
-      </c>
-      <c r="H23" s="85" t="s">
-        <v>50</v>
-      </c>
-      <c r="I23" s="85" t="s">
-        <v>51</v>
-      </c>
-      <c r="J23" s="85" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10">
-      <c r="A24" s="158" t="s">
-        <v>88</v>
-      </c>
-      <c r="B24" s="158"/>
-      <c r="C24" s="158"/>
-      <c r="D24" s="158"/>
-      <c r="E24" s="158"/>
-      <c r="F24" s="158"/>
-      <c r="G24" s="158"/>
-      <c r="H24" s="158"/>
-      <c r="I24" s="158"/>
-      <c r="J24" s="158"/>
+      <c r="I25" s="99">
+        <v>0</v>
+      </c>
+      <c r="J25" s="167"/>
+      <c r="K25" s="167"/>
+    </row>
+    <row r="27" spans="1:37" ht="15.75">
+      <c r="B27" s="73" t="s">
+        <v>66</v>
+      </c>
+      <c r="C27" s="74"/>
+      <c r="D27" s="74"/>
+      <c r="E27" s="74"/>
+      <c r="F27" s="74"/>
+      <c r="G27" s="74"/>
+      <c r="H27" s="74"/>
+      <c r="I27" s="74"/>
+      <c r="J27" s="74"/>
+      <c r="K27" s="74"/>
+    </row>
+    <row r="28" spans="1:37" ht="15.6" customHeight="1">
+      <c r="B28" s="69" t="s">
+        <v>16</v>
+      </c>
+      <c r="C28" s="163" t="s">
+        <v>67</v>
+      </c>
+      <c r="D28" s="163"/>
+      <c r="E28" s="163"/>
+      <c r="F28" s="155" t="s">
+        <v>68</v>
+      </c>
+      <c r="G28" s="156"/>
+      <c r="H28" s="70" t="s">
+        <v>69</v>
+      </c>
+      <c r="I28" s="69" t="s">
+        <v>70</v>
+      </c>
+      <c r="J28" s="69" t="s">
+        <v>71</v>
+      </c>
+      <c r="K28" s="69" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="29" spans="1:37" ht="15.6" customHeight="1">
+      <c r="B29" s="173" t="s">
+        <v>73</v>
+      </c>
+      <c r="C29" s="174"/>
+      <c r="D29" s="174"/>
+      <c r="E29" s="175"/>
+      <c r="F29" s="176"/>
+      <c r="G29" s="177"/>
+      <c r="H29" s="178"/>
+      <c r="I29" s="179"/>
+      <c r="J29" s="179"/>
+      <c r="K29" s="179"/>
+    </row>
+    <row r="30" spans="1:37" s="67" customFormat="1" ht="15.6" customHeight="1">
+      <c r="A30" s="28"/>
+      <c r="B30" s="2"/>
+      <c r="C30" s="2"/>
+      <c r="D30" s="2"/>
+      <c r="E30" s="2"/>
+      <c r="F30" s="75"/>
+      <c r="G30" s="2"/>
+      <c r="H30" s="2"/>
+      <c r="I30" s="2"/>
+      <c r="J30" s="2"/>
+      <c r="K30" s="2"/>
+      <c r="N30" s="2"/>
+      <c r="O30" s="2"/>
+      <c r="P30" s="2"/>
+      <c r="Q30" s="2"/>
+      <c r="R30" s="2"/>
+    </row>
+    <row r="31" spans="1:37" s="67" customFormat="1" ht="15.6" customHeight="1">
+      <c r="A31" s="28"/>
+      <c r="B31" s="2"/>
+      <c r="C31" s="2"/>
+      <c r="D31" s="2"/>
+      <c r="E31" s="2"/>
+      <c r="F31" s="75"/>
+      <c r="G31" s="2"/>
+      <c r="H31" s="2"/>
+      <c r="I31" s="2"/>
+      <c r="J31" s="2"/>
+      <c r="K31" s="2"/>
+      <c r="N31" s="2"/>
+      <c r="O31" s="2"/>
+      <c r="P31" s="2"/>
+      <c r="Q31" s="2"/>
+      <c r="R31" s="2"/>
+    </row>
+    <row r="32" spans="1:37" s="67" customFormat="1" ht="15.6" customHeight="1">
+      <c r="A32" s="28"/>
+      <c r="B32" s="2"/>
+      <c r="C32" s="2"/>
+      <c r="D32" s="2"/>
+      <c r="E32" s="2"/>
+      <c r="F32" s="75"/>
+      <c r="G32" s="2"/>
+      <c r="H32" s="2"/>
+      <c r="I32" s="2"/>
+      <c r="J32" s="2"/>
+      <c r="K32" s="2"/>
+      <c r="N32" s="2"/>
+      <c r="O32" s="2"/>
+      <c r="P32" s="2"/>
+      <c r="Q32" s="2"/>
+      <c r="R32" s="2"/>
     </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="A24:J24"/>
+  <mergeCells count="11">
+    <mergeCell ref="J21:J25"/>
+    <mergeCell ref="K21:K25"/>
+    <mergeCell ref="B29:E29"/>
+    <mergeCell ref="B1:K1"/>
+    <mergeCell ref="H8:K8"/>
+    <mergeCell ref="H9:K9"/>
+    <mergeCell ref="G12:K12"/>
+    <mergeCell ref="G17:K17"/>
+    <mergeCell ref="C28:E28"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="F29:G29"/>
   </mergeCells>
-  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup scale="56" orientation="landscape" horizontalDpi="4294967292" verticalDpi="0" r:id="rId1"/>
+  <drawing r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
@@ -6624,7 +7076,7 @@
     <row r="1" spans="1:9" ht="26.25">
       <c r="A1" s="30"/>
       <c r="B1" s="31" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C1" s="32"/>
       <c r="D1" s="33"/>
@@ -6646,25 +7098,25 @@
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="38" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B3" s="39" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C3" s="40" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D3" s="40" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E3" s="40" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F3" s="40" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="G3" s="40" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="H3" s="33"/>
     </row>
@@ -6677,10 +7129,10 @@
         <v>1</v>
       </c>
       <c r="D4" s="44" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E4" s="45" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F4" s="46"/>
       <c r="G4" s="47"/>
@@ -6706,13 +7158,13 @@
       <c r="G6" s="52"/>
     </row>
     <row r="12" spans="1:9">
-      <c r="F12" s="122"/>
+      <c r="F12" s="129"/>
     </row>
     <row r="13" spans="1:9">
-      <c r="F13" s="122"/>
+      <c r="F13" s="129"/>
     </row>
     <row r="14" spans="1:9">
-      <c r="F14" s="122"/>
+      <c r="F14" s="129"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -6737,405 +7189,458 @@
   <sheetData>
     <row r="1" spans="2:18" ht="15.75" thickBot="1"/>
     <row r="2" spans="2:18" ht="30.95" customHeight="1" thickBot="1">
-      <c r="B2" s="134" t="s">
-        <v>21</v>
-      </c>
-      <c r="C2" s="135"/>
-      <c r="D2" s="135" t="s">
-        <v>22</v>
-      </c>
-      <c r="E2" s="135"/>
-      <c r="F2" s="135"/>
-      <c r="G2" s="135" t="s">
-        <v>23</v>
-      </c>
-      <c r="H2" s="135"/>
-      <c r="I2" s="135"/>
-      <c r="J2" s="135"/>
-      <c r="K2" s="135"/>
-      <c r="L2" s="135"/>
-      <c r="M2" s="135"/>
-      <c r="N2" s="135"/>
-      <c r="O2" s="135"/>
-      <c r="P2" s="135" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q2" s="135"/>
-      <c r="R2" s="136"/>
+      <c r="B2" s="130" t="s">
+        <v>25</v>
+      </c>
+      <c r="C2" s="131"/>
+      <c r="D2" s="131" t="s">
+        <v>26</v>
+      </c>
+      <c r="E2" s="131"/>
+      <c r="F2" s="131"/>
+      <c r="G2" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="H2" s="131"/>
+      <c r="I2" s="131"/>
+      <c r="J2" s="131"/>
+      <c r="K2" s="131"/>
+      <c r="L2" s="131"/>
+      <c r="M2" s="131"/>
+      <c r="N2" s="131"/>
+      <c r="O2" s="131"/>
+      <c r="P2" s="131" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q2" s="131"/>
+      <c r="R2" s="132"/>
     </row>
     <row r="3" spans="2:18">
-      <c r="B3" s="137" t="s">
-        <v>25</v>
-      </c>
-      <c r="C3" s="138"/>
-      <c r="D3" s="139">
+      <c r="B3" s="133" t="s">
+        <v>29</v>
+      </c>
+      <c r="C3" s="134"/>
+      <c r="D3" s="135">
         <v>43825</v>
       </c>
-      <c r="E3" s="140"/>
-      <c r="F3" s="140"/>
-      <c r="G3" s="141" t="s">
-        <v>26</v>
-      </c>
-      <c r="H3" s="142"/>
-      <c r="I3" s="142"/>
-      <c r="J3" s="142"/>
-      <c r="K3" s="142"/>
-      <c r="L3" s="142"/>
-      <c r="M3" s="142"/>
-      <c r="N3" s="142"/>
-      <c r="O3" s="142"/>
-      <c r="P3" s="143" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q3" s="143"/>
-      <c r="R3" s="144"/>
+      <c r="E3" s="136"/>
+      <c r="F3" s="136"/>
+      <c r="G3" s="137" t="s">
+        <v>30</v>
+      </c>
+      <c r="H3" s="138"/>
+      <c r="I3" s="138"/>
+      <c r="J3" s="138"/>
+      <c r="K3" s="138"/>
+      <c r="L3" s="138"/>
+      <c r="M3" s="138"/>
+      <c r="N3" s="138"/>
+      <c r="O3" s="138"/>
+      <c r="P3" s="139" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q3" s="139"/>
+      <c r="R3" s="140"/>
     </row>
     <row r="4" spans="2:18">
-      <c r="B4" s="129" t="s">
-        <v>28</v>
-      </c>
-      <c r="C4" s="130"/>
-      <c r="D4" s="131"/>
-      <c r="E4" s="131"/>
-      <c r="F4" s="131"/>
-      <c r="G4" s="132" t="s">
-        <v>29</v>
-      </c>
-      <c r="H4" s="132"/>
-      <c r="I4" s="132"/>
-      <c r="J4" s="132"/>
-      <c r="K4" s="132"/>
-      <c r="L4" s="132"/>
-      <c r="M4" s="132"/>
-      <c r="N4" s="132"/>
-      <c r="O4" s="132"/>
-      <c r="P4" s="131" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q4" s="131"/>
-      <c r="R4" s="133"/>
+      <c r="B4" s="141" t="s">
+        <v>32</v>
+      </c>
+      <c r="C4" s="142"/>
+      <c r="D4" s="143"/>
+      <c r="E4" s="143"/>
+      <c r="F4" s="143"/>
+      <c r="G4" s="144" t="s">
+        <v>33</v>
+      </c>
+      <c r="H4" s="144"/>
+      <c r="I4" s="144"/>
+      <c r="J4" s="144"/>
+      <c r="K4" s="144"/>
+      <c r="L4" s="144"/>
+      <c r="M4" s="144"/>
+      <c r="N4" s="144"/>
+      <c r="O4" s="144"/>
+      <c r="P4" s="143" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q4" s="143"/>
+      <c r="R4" s="145"/>
     </row>
     <row r="5" spans="2:18" ht="17.25" customHeight="1">
-      <c r="B5" s="129"/>
-      <c r="C5" s="130"/>
-      <c r="D5" s="131"/>
-      <c r="E5" s="131"/>
-      <c r="F5" s="131"/>
-      <c r="G5" s="132"/>
-      <c r="H5" s="132"/>
-      <c r="I5" s="132"/>
-      <c r="J5" s="132"/>
-      <c r="K5" s="132"/>
-      <c r="L5" s="132"/>
-      <c r="M5" s="132"/>
-      <c r="N5" s="132"/>
-      <c r="O5" s="132"/>
-      <c r="P5" s="131"/>
-      <c r="Q5" s="131"/>
-      <c r="R5" s="133"/>
+      <c r="B5" s="141"/>
+      <c r="C5" s="142"/>
+      <c r="D5" s="143"/>
+      <c r="E5" s="143"/>
+      <c r="F5" s="143"/>
+      <c r="G5" s="144"/>
+      <c r="H5" s="144"/>
+      <c r="I5" s="144"/>
+      <c r="J5" s="144"/>
+      <c r="K5" s="144"/>
+      <c r="L5" s="144"/>
+      <c r="M5" s="144"/>
+      <c r="N5" s="144"/>
+      <c r="O5" s="144"/>
+      <c r="P5" s="143"/>
+      <c r="Q5" s="143"/>
+      <c r="R5" s="145"/>
     </row>
     <row r="6" spans="2:18" ht="17.25" customHeight="1">
-      <c r="B6" s="129"/>
-      <c r="C6" s="130"/>
-      <c r="D6" s="131"/>
-      <c r="E6" s="131"/>
-      <c r="F6" s="131"/>
-      <c r="G6" s="132"/>
-      <c r="H6" s="132"/>
-      <c r="I6" s="132"/>
-      <c r="J6" s="132"/>
-      <c r="K6" s="132"/>
-      <c r="L6" s="132"/>
-      <c r="M6" s="132"/>
-      <c r="N6" s="132"/>
-      <c r="O6" s="132"/>
-      <c r="P6" s="131"/>
-      <c r="Q6" s="131"/>
-      <c r="R6" s="133"/>
+      <c r="B6" s="141"/>
+      <c r="C6" s="142"/>
+      <c r="D6" s="143"/>
+      <c r="E6" s="143"/>
+      <c r="F6" s="143"/>
+      <c r="G6" s="144"/>
+      <c r="H6" s="144"/>
+      <c r="I6" s="144"/>
+      <c r="J6" s="144"/>
+      <c r="K6" s="144"/>
+      <c r="L6" s="144"/>
+      <c r="M6" s="144"/>
+      <c r="N6" s="144"/>
+      <c r="O6" s="144"/>
+      <c r="P6" s="143"/>
+      <c r="Q6" s="143"/>
+      <c r="R6" s="145"/>
     </row>
     <row r="7" spans="2:18">
-      <c r="B7" s="129"/>
-      <c r="C7" s="130"/>
-      <c r="D7" s="131"/>
-      <c r="E7" s="131"/>
-      <c r="F7" s="131"/>
-      <c r="G7" s="132"/>
-      <c r="H7" s="132"/>
-      <c r="I7" s="132"/>
-      <c r="J7" s="132"/>
-      <c r="K7" s="132"/>
-      <c r="L7" s="132"/>
-      <c r="M7" s="132"/>
-      <c r="N7" s="132"/>
-      <c r="O7" s="132"/>
-      <c r="P7" s="131"/>
-      <c r="Q7" s="131"/>
-      <c r="R7" s="133"/>
+      <c r="B7" s="141"/>
+      <c r="C7" s="142"/>
+      <c r="D7" s="143"/>
+      <c r="E7" s="143"/>
+      <c r="F7" s="143"/>
+      <c r="G7" s="144"/>
+      <c r="H7" s="144"/>
+      <c r="I7" s="144"/>
+      <c r="J7" s="144"/>
+      <c r="K7" s="144"/>
+      <c r="L7" s="144"/>
+      <c r="M7" s="144"/>
+      <c r="N7" s="144"/>
+      <c r="O7" s="144"/>
+      <c r="P7" s="143"/>
+      <c r="Q7" s="143"/>
+      <c r="R7" s="145"/>
     </row>
     <row r="8" spans="2:18">
-      <c r="B8" s="129"/>
-      <c r="C8" s="130"/>
-      <c r="D8" s="131"/>
-      <c r="E8" s="131"/>
-      <c r="F8" s="131"/>
-      <c r="G8" s="132"/>
-      <c r="H8" s="132"/>
-      <c r="I8" s="132"/>
-      <c r="J8" s="132"/>
-      <c r="K8" s="132"/>
-      <c r="L8" s="132"/>
-      <c r="M8" s="132"/>
-      <c r="N8" s="132"/>
-      <c r="O8" s="132"/>
-      <c r="P8" s="131"/>
-      <c r="Q8" s="131"/>
-      <c r="R8" s="133"/>
+      <c r="B8" s="141"/>
+      <c r="C8" s="142"/>
+      <c r="D8" s="143"/>
+      <c r="E8" s="143"/>
+      <c r="F8" s="143"/>
+      <c r="G8" s="144"/>
+      <c r="H8" s="144"/>
+      <c r="I8" s="144"/>
+      <c r="J8" s="144"/>
+      <c r="K8" s="144"/>
+      <c r="L8" s="144"/>
+      <c r="M8" s="144"/>
+      <c r="N8" s="144"/>
+      <c r="O8" s="144"/>
+      <c r="P8" s="143"/>
+      <c r="Q8" s="143"/>
+      <c r="R8" s="145"/>
     </row>
     <row r="9" spans="2:18">
-      <c r="B9" s="129"/>
-      <c r="C9" s="130"/>
-      <c r="D9" s="131"/>
-      <c r="E9" s="131"/>
-      <c r="F9" s="131"/>
-      <c r="G9" s="132"/>
-      <c r="H9" s="132"/>
-      <c r="I9" s="132"/>
-      <c r="J9" s="132"/>
-      <c r="K9" s="132"/>
-      <c r="L9" s="132"/>
-      <c r="M9" s="132"/>
-      <c r="N9" s="132"/>
-      <c r="O9" s="132"/>
-      <c r="P9" s="131"/>
-      <c r="Q9" s="131"/>
-      <c r="R9" s="133"/>
+      <c r="B9" s="141"/>
+      <c r="C9" s="142"/>
+      <c r="D9" s="143"/>
+      <c r="E9" s="143"/>
+      <c r="F9" s="143"/>
+      <c r="G9" s="144"/>
+      <c r="H9" s="144"/>
+      <c r="I9" s="144"/>
+      <c r="J9" s="144"/>
+      <c r="K9" s="144"/>
+      <c r="L9" s="144"/>
+      <c r="M9" s="144"/>
+      <c r="N9" s="144"/>
+      <c r="O9" s="144"/>
+      <c r="P9" s="143"/>
+      <c r="Q9" s="143"/>
+      <c r="R9" s="145"/>
     </row>
     <row r="10" spans="2:18">
-      <c r="B10" s="129"/>
-      <c r="C10" s="130"/>
-      <c r="D10" s="131"/>
-      <c r="E10" s="131"/>
-      <c r="F10" s="131"/>
-      <c r="G10" s="132"/>
-      <c r="H10" s="132"/>
-      <c r="I10" s="132"/>
-      <c r="J10" s="132"/>
-      <c r="K10" s="132"/>
-      <c r="L10" s="132"/>
-      <c r="M10" s="132"/>
-      <c r="N10" s="132"/>
-      <c r="O10" s="132"/>
-      <c r="P10" s="131"/>
-      <c r="Q10" s="131"/>
-      <c r="R10" s="133"/>
+      <c r="B10" s="141"/>
+      <c r="C10" s="142"/>
+      <c r="D10" s="143"/>
+      <c r="E10" s="143"/>
+      <c r="F10" s="143"/>
+      <c r="G10" s="144"/>
+      <c r="H10" s="144"/>
+      <c r="I10" s="144"/>
+      <c r="J10" s="144"/>
+      <c r="K10" s="144"/>
+      <c r="L10" s="144"/>
+      <c r="M10" s="144"/>
+      <c r="N10" s="144"/>
+      <c r="O10" s="144"/>
+      <c r="P10" s="143"/>
+      <c r="Q10" s="143"/>
+      <c r="R10" s="145"/>
     </row>
     <row r="11" spans="2:18">
-      <c r="B11" s="129"/>
-      <c r="C11" s="130"/>
-      <c r="D11" s="131"/>
-      <c r="E11" s="131"/>
-      <c r="F11" s="131"/>
-      <c r="G11" s="132"/>
-      <c r="H11" s="132"/>
-      <c r="I11" s="132"/>
-      <c r="J11" s="132"/>
-      <c r="K11" s="132"/>
-      <c r="L11" s="132"/>
-      <c r="M11" s="132"/>
-      <c r="N11" s="132"/>
-      <c r="O11" s="132"/>
-      <c r="P11" s="131"/>
-      <c r="Q11" s="131"/>
-      <c r="R11" s="133"/>
+      <c r="B11" s="141"/>
+      <c r="C11" s="142"/>
+      <c r="D11" s="143"/>
+      <c r="E11" s="143"/>
+      <c r="F11" s="143"/>
+      <c r="G11" s="144"/>
+      <c r="H11" s="144"/>
+      <c r="I11" s="144"/>
+      <c r="J11" s="144"/>
+      <c r="K11" s="144"/>
+      <c r="L11" s="144"/>
+      <c r="M11" s="144"/>
+      <c r="N11" s="144"/>
+      <c r="O11" s="144"/>
+      <c r="P11" s="143"/>
+      <c r="Q11" s="143"/>
+      <c r="R11" s="145"/>
     </row>
     <row r="12" spans="2:18">
-      <c r="B12" s="129"/>
-      <c r="C12" s="130"/>
-      <c r="D12" s="131"/>
-      <c r="E12" s="131"/>
-      <c r="F12" s="131"/>
-      <c r="G12" s="132"/>
-      <c r="H12" s="132"/>
-      <c r="I12" s="132"/>
-      <c r="J12" s="132"/>
-      <c r="K12" s="132"/>
-      <c r="L12" s="132"/>
-      <c r="M12" s="132"/>
-      <c r="N12" s="132"/>
-      <c r="O12" s="132"/>
-      <c r="P12" s="131"/>
-      <c r="Q12" s="131"/>
-      <c r="R12" s="133"/>
+      <c r="B12" s="141"/>
+      <c r="C12" s="142"/>
+      <c r="D12" s="143"/>
+      <c r="E12" s="143"/>
+      <c r="F12" s="143"/>
+      <c r="G12" s="144"/>
+      <c r="H12" s="144"/>
+      <c r="I12" s="144"/>
+      <c r="J12" s="144"/>
+      <c r="K12" s="144"/>
+      <c r="L12" s="144"/>
+      <c r="M12" s="144"/>
+      <c r="N12" s="144"/>
+      <c r="O12" s="144"/>
+      <c r="P12" s="143"/>
+      <c r="Q12" s="143"/>
+      <c r="R12" s="145"/>
     </row>
     <row r="13" spans="2:18">
-      <c r="B13" s="129"/>
-      <c r="C13" s="130"/>
-      <c r="D13" s="131"/>
-      <c r="E13" s="131"/>
-      <c r="F13" s="131"/>
-      <c r="G13" s="132"/>
-      <c r="H13" s="132"/>
-      <c r="I13" s="132"/>
-      <c r="J13" s="132"/>
-      <c r="K13" s="132"/>
-      <c r="L13" s="132"/>
-      <c r="M13" s="132"/>
-      <c r="N13" s="132"/>
-      <c r="O13" s="132"/>
-      <c r="P13" s="131"/>
-      <c r="Q13" s="131"/>
-      <c r="R13" s="133"/>
+      <c r="B13" s="141"/>
+      <c r="C13" s="142"/>
+      <c r="D13" s="143"/>
+      <c r="E13" s="143"/>
+      <c r="F13" s="143"/>
+      <c r="G13" s="144"/>
+      <c r="H13" s="144"/>
+      <c r="I13" s="144"/>
+      <c r="J13" s="144"/>
+      <c r="K13" s="144"/>
+      <c r="L13" s="144"/>
+      <c r="M13" s="144"/>
+      <c r="N13" s="144"/>
+      <c r="O13" s="144"/>
+      <c r="P13" s="143"/>
+      <c r="Q13" s="143"/>
+      <c r="R13" s="145"/>
     </row>
     <row r="14" spans="2:18">
-      <c r="B14" s="129"/>
-      <c r="C14" s="130"/>
-      <c r="D14" s="131"/>
-      <c r="E14" s="131"/>
-      <c r="F14" s="131"/>
-      <c r="G14" s="132"/>
-      <c r="H14" s="132"/>
-      <c r="I14" s="132"/>
-      <c r="J14" s="132"/>
-      <c r="K14" s="132"/>
-      <c r="L14" s="132"/>
-      <c r="M14" s="132"/>
-      <c r="N14" s="132"/>
-      <c r="O14" s="132"/>
-      <c r="P14" s="131"/>
-      <c r="Q14" s="131"/>
-      <c r="R14" s="133"/>
+      <c r="B14" s="141"/>
+      <c r="C14" s="142"/>
+      <c r="D14" s="143"/>
+      <c r="E14" s="143"/>
+      <c r="F14" s="143"/>
+      <c r="G14" s="144"/>
+      <c r="H14" s="144"/>
+      <c r="I14" s="144"/>
+      <c r="J14" s="144"/>
+      <c r="K14" s="144"/>
+      <c r="L14" s="144"/>
+      <c r="M14" s="144"/>
+      <c r="N14" s="144"/>
+      <c r="O14" s="144"/>
+      <c r="P14" s="143"/>
+      <c r="Q14" s="143"/>
+      <c r="R14" s="145"/>
     </row>
     <row r="15" spans="2:18">
-      <c r="B15" s="129"/>
-      <c r="C15" s="130"/>
-      <c r="D15" s="131"/>
-      <c r="E15" s="131"/>
-      <c r="F15" s="131"/>
-      <c r="G15" s="132"/>
-      <c r="H15" s="132"/>
-      <c r="I15" s="132"/>
-      <c r="J15" s="132"/>
-      <c r="K15" s="132"/>
-      <c r="L15" s="132"/>
-      <c r="M15" s="132"/>
-      <c r="N15" s="132"/>
-      <c r="O15" s="132"/>
-      <c r="P15" s="131"/>
-      <c r="Q15" s="131"/>
-      <c r="R15" s="133"/>
+      <c r="B15" s="141"/>
+      <c r="C15" s="142"/>
+      <c r="D15" s="143"/>
+      <c r="E15" s="143"/>
+      <c r="F15" s="143"/>
+      <c r="G15" s="144"/>
+      <c r="H15" s="144"/>
+      <c r="I15" s="144"/>
+      <c r="J15" s="144"/>
+      <c r="K15" s="144"/>
+      <c r="L15" s="144"/>
+      <c r="M15" s="144"/>
+      <c r="N15" s="144"/>
+      <c r="O15" s="144"/>
+      <c r="P15" s="143"/>
+      <c r="Q15" s="143"/>
+      <c r="R15" s="145"/>
     </row>
     <row r="16" spans="2:18" ht="15.75" thickBot="1">
-      <c r="B16" s="123"/>
-      <c r="C16" s="124"/>
-      <c r="D16" s="125"/>
-      <c r="E16" s="125"/>
-      <c r="F16" s="125"/>
-      <c r="G16" s="126"/>
-      <c r="H16" s="126"/>
-      <c r="I16" s="126"/>
-      <c r="J16" s="126"/>
-      <c r="K16" s="126"/>
-      <c r="L16" s="126"/>
-      <c r="M16" s="126"/>
-      <c r="N16" s="126"/>
-      <c r="O16" s="126"/>
-      <c r="P16" s="125"/>
-      <c r="Q16" s="125"/>
-      <c r="R16" s="127"/>
+      <c r="B16" s="146"/>
+      <c r="C16" s="147"/>
+      <c r="D16" s="148"/>
+      <c r="E16" s="148"/>
+      <c r="F16" s="148"/>
+      <c r="G16" s="149"/>
+      <c r="H16" s="149"/>
+      <c r="I16" s="149"/>
+      <c r="J16" s="149"/>
+      <c r="K16" s="149"/>
+      <c r="L16" s="149"/>
+      <c r="M16" s="149"/>
+      <c r="N16" s="149"/>
+      <c r="O16" s="149"/>
+      <c r="P16" s="148"/>
+      <c r="Q16" s="148"/>
+      <c r="R16" s="150"/>
     </row>
     <row r="18" spans="1:19">
       <c r="A18" s="5" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
     </row>
     <row r="19" spans="1:19">
-      <c r="A19" s="128" t="s">
-        <v>32</v>
-      </c>
-      <c r="B19" s="128"/>
-      <c r="C19" s="128"/>
-      <c r="D19" s="128"/>
-      <c r="E19" s="128"/>
-      <c r="F19" s="128"/>
-      <c r="G19" s="128"/>
-      <c r="H19" s="128"/>
-      <c r="I19" s="128"/>
-      <c r="J19" s="128"/>
-      <c r="K19" s="128"/>
-      <c r="L19" s="128"/>
-      <c r="M19" s="128"/>
-      <c r="N19" s="128"/>
-      <c r="O19" s="128"/>
-      <c r="P19" s="128"/>
-      <c r="Q19" s="128"/>
-      <c r="R19" s="128"/>
-      <c r="S19" s="128"/>
+      <c r="A19" s="151" t="s">
+        <v>36</v>
+      </c>
+      <c r="B19" s="151"/>
+      <c r="C19" s="151"/>
+      <c r="D19" s="151"/>
+      <c r="E19" s="151"/>
+      <c r="F19" s="151"/>
+      <c r="G19" s="151"/>
+      <c r="H19" s="151"/>
+      <c r="I19" s="151"/>
+      <c r="J19" s="151"/>
+      <c r="K19" s="151"/>
+      <c r="L19" s="151"/>
+      <c r="M19" s="151"/>
+      <c r="N19" s="151"/>
+      <c r="O19" s="151"/>
+      <c r="P19" s="151"/>
+      <c r="Q19" s="151"/>
+      <c r="R19" s="151"/>
+      <c r="S19" s="151"/>
     </row>
     <row r="20" spans="1:19">
-      <c r="A20" s="128"/>
-      <c r="B20" s="128"/>
-      <c r="C20" s="128"/>
-      <c r="D20" s="128"/>
-      <c r="E20" s="128"/>
-      <c r="F20" s="128"/>
-      <c r="G20" s="128"/>
-      <c r="H20" s="128"/>
-      <c r="I20" s="128"/>
-      <c r="J20" s="128"/>
-      <c r="K20" s="128"/>
-      <c r="L20" s="128"/>
-      <c r="M20" s="128"/>
-      <c r="N20" s="128"/>
-      <c r="O20" s="128"/>
-      <c r="P20" s="128"/>
-      <c r="Q20" s="128"/>
-      <c r="R20" s="128"/>
-      <c r="S20" s="128"/>
+      <c r="A20" s="151"/>
+      <c r="B20" s="151"/>
+      <c r="C20" s="151"/>
+      <c r="D20" s="151"/>
+      <c r="E20" s="151"/>
+      <c r="F20" s="151"/>
+      <c r="G20" s="151"/>
+      <c r="H20" s="151"/>
+      <c r="I20" s="151"/>
+      <c r="J20" s="151"/>
+      <c r="K20" s="151"/>
+      <c r="L20" s="151"/>
+      <c r="M20" s="151"/>
+      <c r="N20" s="151"/>
+      <c r="O20" s="151"/>
+      <c r="P20" s="151"/>
+      <c r="Q20" s="151"/>
+      <c r="R20" s="151"/>
+      <c r="S20" s="151"/>
     </row>
     <row r="21" spans="1:19">
-      <c r="A21" s="128"/>
-      <c r="B21" s="128"/>
-      <c r="C21" s="128"/>
-      <c r="D21" s="128"/>
-      <c r="E21" s="128"/>
-      <c r="F21" s="128"/>
-      <c r="G21" s="128"/>
-      <c r="H21" s="128"/>
-      <c r="I21" s="128"/>
-      <c r="J21" s="128"/>
-      <c r="K21" s="128"/>
-      <c r="L21" s="128"/>
-      <c r="M21" s="128"/>
-      <c r="N21" s="128"/>
-      <c r="O21" s="128"/>
-      <c r="P21" s="128"/>
-      <c r="Q21" s="128"/>
-      <c r="R21" s="128"/>
-      <c r="S21" s="128"/>
+      <c r="A21" s="151"/>
+      <c r="B21" s="151"/>
+      <c r="C21" s="151"/>
+      <c r="D21" s="151"/>
+      <c r="E21" s="151"/>
+      <c r="F21" s="151"/>
+      <c r="G21" s="151"/>
+      <c r="H21" s="151"/>
+      <c r="I21" s="151"/>
+      <c r="J21" s="151"/>
+      <c r="K21" s="151"/>
+      <c r="L21" s="151"/>
+      <c r="M21" s="151"/>
+      <c r="N21" s="151"/>
+      <c r="O21" s="151"/>
+      <c r="P21" s="151"/>
+      <c r="Q21" s="151"/>
+      <c r="R21" s="151"/>
+      <c r="S21" s="151"/>
     </row>
     <row r="22" spans="1:19">
-      <c r="A22" s="128"/>
-      <c r="B22" s="128"/>
-      <c r="C22" s="128"/>
-      <c r="D22" s="128"/>
-      <c r="E22" s="128"/>
-      <c r="F22" s="128"/>
-      <c r="G22" s="128"/>
-      <c r="H22" s="128"/>
-      <c r="I22" s="128"/>
-      <c r="J22" s="128"/>
-      <c r="K22" s="128"/>
-      <c r="L22" s="128"/>
-      <c r="M22" s="128"/>
-      <c r="N22" s="128"/>
-      <c r="O22" s="128"/>
-      <c r="P22" s="128"/>
-      <c r="Q22" s="128"/>
-      <c r="R22" s="128"/>
-      <c r="S22" s="128"/>
+      <c r="A22" s="151"/>
+      <c r="B22" s="151"/>
+      <c r="C22" s="151"/>
+      <c r="D22" s="151"/>
+      <c r="E22" s="151"/>
+      <c r="F22" s="151"/>
+      <c r="G22" s="151"/>
+      <c r="H22" s="151"/>
+      <c r="I22" s="151"/>
+      <c r="J22" s="151"/>
+      <c r="K22" s="151"/>
+      <c r="L22" s="151"/>
+      <c r="M22" s="151"/>
+      <c r="N22" s="151"/>
+      <c r="O22" s="151"/>
+      <c r="P22" s="151"/>
+      <c r="Q22" s="151"/>
+      <c r="R22" s="151"/>
+      <c r="S22" s="151"/>
     </row>
   </sheetData>
   <mergeCells count="61">
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="G16:O16"/>
+    <mergeCell ref="P16:R16"/>
+    <mergeCell ref="A19:S22"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="G14:O14"/>
+    <mergeCell ref="P14:R14"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="G15:O15"/>
+    <mergeCell ref="P15:R15"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="D12:F12"/>
+    <mergeCell ref="G12:O12"/>
+    <mergeCell ref="P12:R12"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="G13:O13"/>
+    <mergeCell ref="P13:R13"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="D10:F10"/>
+    <mergeCell ref="G10:O10"/>
+    <mergeCell ref="P10:R10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D11:F11"/>
+    <mergeCell ref="G11:O11"/>
+    <mergeCell ref="P11:R11"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="D8:F8"/>
+    <mergeCell ref="G8:O8"/>
+    <mergeCell ref="P8:R8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="D9:F9"/>
+    <mergeCell ref="G9:O9"/>
+    <mergeCell ref="P9:R9"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="D6:F6"/>
+    <mergeCell ref="G6:O6"/>
+    <mergeCell ref="P6:R6"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="D7:F7"/>
+    <mergeCell ref="G7:O7"/>
+    <mergeCell ref="P7:R7"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="D4:F4"/>
+    <mergeCell ref="G4:O4"/>
+    <mergeCell ref="P4:R4"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="D5:F5"/>
+    <mergeCell ref="G5:O5"/>
+    <mergeCell ref="P5:R5"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="D2:F2"/>
     <mergeCell ref="G2:O2"/>
@@ -7144,59 +7649,6 @@
     <mergeCell ref="D3:F3"/>
     <mergeCell ref="G3:O3"/>
     <mergeCell ref="P3:R3"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="D4:F4"/>
-    <mergeCell ref="G4:O4"/>
-    <mergeCell ref="P4:R4"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="D5:F5"/>
-    <mergeCell ref="G5:O5"/>
-    <mergeCell ref="P5:R5"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="D6:F6"/>
-    <mergeCell ref="G6:O6"/>
-    <mergeCell ref="P6:R6"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="D7:F7"/>
-    <mergeCell ref="G7:O7"/>
-    <mergeCell ref="P7:R7"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="D8:F8"/>
-    <mergeCell ref="G8:O8"/>
-    <mergeCell ref="P8:R8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D9:F9"/>
-    <mergeCell ref="G9:O9"/>
-    <mergeCell ref="P9:R9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="D10:F10"/>
-    <mergeCell ref="G10:O10"/>
-    <mergeCell ref="P10:R10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="D11:F11"/>
-    <mergeCell ref="G11:O11"/>
-    <mergeCell ref="P11:R11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="D12:F12"/>
-    <mergeCell ref="G12:O12"/>
-    <mergeCell ref="P12:R12"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="D13:F13"/>
-    <mergeCell ref="G13:O13"/>
-    <mergeCell ref="P13:R13"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="D14:F14"/>
-    <mergeCell ref="G14:O14"/>
-    <mergeCell ref="P14:R14"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="D15:F15"/>
-    <mergeCell ref="G15:O15"/>
-    <mergeCell ref="P15:R15"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="D16:F16"/>
-    <mergeCell ref="G16:O16"/>
-    <mergeCell ref="P16:R16"/>
-    <mergeCell ref="A19:S22"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" fitToWidth="0" fitToHeight="0" orientation="landscape" r:id="rId1"/>
@@ -7229,18 +7681,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:37" ht="24" customHeight="1">
-      <c r="B1" s="148" t="s">
-        <v>68</v>
-      </c>
-      <c r="C1" s="148"/>
-      <c r="D1" s="148"/>
-      <c r="E1" s="148"/>
-      <c r="F1" s="148"/>
-      <c r="G1" s="148"/>
-      <c r="H1" s="148"/>
-      <c r="I1" s="148"/>
-      <c r="J1" s="148"/>
-      <c r="K1" s="148"/>
+      <c r="B1" s="102" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1" s="102"/>
+      <c r="D1" s="102"/>
+      <c r="E1" s="102"/>
+      <c r="F1" s="102"/>
+      <c r="G1" s="102"/>
+      <c r="H1" s="102"/>
+      <c r="I1" s="102"/>
+      <c r="J1" s="102"/>
+      <c r="K1" s="102"/>
       <c r="L1" s="63"/>
       <c r="M1" s="63"/>
       <c r="N1" s="63"/>
@@ -7266,7 +7718,7 @@
     </row>
     <row r="3" spans="2:37" ht="15.6" customHeight="1">
       <c r="B3" s="3" t="s">
-        <v>67</v>
+        <v>38</v>
       </c>
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
@@ -7274,7 +7726,7 @@
     </row>
     <row r="4" spans="2:37" ht="15.6" customHeight="1">
       <c r="B4" s="3" t="s">
-        <v>69</v>
+        <v>39</v>
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
@@ -7282,14 +7734,14 @@
     </row>
     <row r="5" spans="2:37" ht="15.6" customHeight="1">
       <c r="B5" s="3" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="C5" s="3"/>
       <c r="D5" s="80">
         <v>46147</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>66</v>
+        <v>41</v>
       </c>
       <c r="G5" s="62"/>
       <c r="H5" s="62"/>
@@ -7313,7 +7765,7 @@
     </row>
     <row r="7" spans="2:37" ht="15.6" customHeight="1">
       <c r="B7" s="73" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="C7" s="74"/>
       <c r="D7" s="74"/>
@@ -7322,7 +7774,7 @@
       <c r="G7" s="74"/>
       <c r="H7" s="74"/>
       <c r="I7" s="74" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="J7" s="74"/>
       <c r="K7" s="74"/>
@@ -7355,13 +7807,13 @@
     </row>
     <row r="8" spans="2:37" s="61" customFormat="1" ht="29.1" customHeight="1">
       <c r="B8" s="72" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C8" s="69" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="D8" s="69" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="E8" s="60"/>
       <c r="F8" s="60"/>
@@ -7376,7 +7828,7 @@
         <v>1</v>
       </c>
       <c r="C9" s="59" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="D9" s="59">
         <v>5</v>
@@ -7430,7 +7882,7 @@
     </row>
     <row r="14" spans="2:37" ht="15.6" customHeight="1">
       <c r="B14" s="73" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="C14" s="74"/>
       <c r="D14" s="74"/>
@@ -7470,28 +7922,28 @@
     </row>
     <row r="15" spans="2:37" ht="35.1" customHeight="1">
       <c r="B15" s="71" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C15" s="71" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="D15" s="71" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="E15" s="71" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="F15" s="77" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="G15" s="69" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="H15" s="71" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="I15" s="71" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="J15" s="1"/>
       <c r="K15" s="1"/>
@@ -7501,25 +7953,25 @@
         <v>1</v>
       </c>
       <c r="C16" s="58" t="s">
+        <v>54</v>
+      </c>
+      <c r="D16" s="58" t="s">
         <v>55</v>
       </c>
-      <c r="D16" s="58" t="s">
+      <c r="E16" s="58" t="s">
         <v>56</v>
       </c>
-      <c r="E16" s="58" t="s">
-        <v>61</v>
-      </c>
       <c r="F16" s="78" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="G16" s="58">
         <v>48</v>
       </c>
       <c r="H16" s="58" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="I16" s="58" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="J16" s="1"/>
       <c r="K16" s="1"/>
@@ -7529,25 +7981,25 @@
         <v>2</v>
       </c>
       <c r="C17" s="58" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D17" s="58" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E17" s="58" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F17" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G17" s="58">
         <v>16</v>
       </c>
       <c r="H17" s="58" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="I17" s="58" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="J17" s="1"/>
       <c r="K17" s="1"/>
@@ -7557,25 +8009,25 @@
         <v>3</v>
       </c>
       <c r="C18" s="58" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D18" s="58" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="E18" s="58" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F18" s="79" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="G18" s="58">
         <v>48</v>
       </c>
       <c r="H18" s="58" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="I18" s="58" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="J18" s="1"/>
       <c r="K18" s="1"/>
@@ -7585,25 +8037,25 @@
         <v>4</v>
       </c>
       <c r="C19" s="58" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D19" s="58" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="E19" s="58" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F19" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G19" s="58">
         <v>16</v>
       </c>
       <c r="H19" s="58" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="I19" s="58" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="J19" s="1"/>
       <c r="K19" s="1"/>
@@ -7613,32 +8065,32 @@
         <v>5</v>
       </c>
       <c r="C20" s="58" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D20" s="58" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E20" s="58" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="F20" s="78" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G20" s="58">
         <v>48</v>
       </c>
       <c r="H20" s="58" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="I20" s="58" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="J20" s="1"/>
       <c r="K20" s="1"/>
     </row>
     <row r="22" spans="1:37" ht="15.6" customHeight="1">
       <c r="B22" s="73" t="s">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="C22" s="74"/>
       <c r="D22" s="74"/>
@@ -7679,28 +8131,28 @@
     <row r="23" spans="1:37" s="67" customFormat="1" ht="15.6" customHeight="1">
       <c r="A23" s="28"/>
       <c r="B23" s="69" t="s">
-        <v>12</v>
-      </c>
-      <c r="C23" s="149" t="s">
-        <v>47</v>
-      </c>
-      <c r="D23" s="153"/>
-      <c r="E23" s="150"/>
-      <c r="F23" s="149" t="s">
-        <v>48</v>
-      </c>
-      <c r="G23" s="150"/>
+        <v>16</v>
+      </c>
+      <c r="C23" s="155" t="s">
+        <v>67</v>
+      </c>
+      <c r="D23" s="159"/>
+      <c r="E23" s="156"/>
+      <c r="F23" s="155" t="s">
+        <v>68</v>
+      </c>
+      <c r="G23" s="156"/>
       <c r="H23" s="70" t="s">
-        <v>49</v>
+        <v>69</v>
       </c>
       <c r="I23" s="69" t="s">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="J23" s="69" t="s">
-        <v>51</v>
+        <v>71</v>
       </c>
       <c r="K23" s="69" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -7713,13 +8165,13 @@
       <c r="B24" s="56">
         <v>1</v>
       </c>
-      <c r="C24" s="145" t="s">
-        <v>53</v>
-      </c>
-      <c r="D24" s="146"/>
-      <c r="E24" s="147"/>
-      <c r="F24" s="151"/>
-      <c r="G24" s="152"/>
+      <c r="C24" s="152" t="s">
+        <v>73</v>
+      </c>
+      <c r="D24" s="153"/>
+      <c r="E24" s="154"/>
+      <c r="F24" s="157"/>
+      <c r="G24" s="158"/>
       <c r="H24" s="68"/>
       <c r="I24" s="57"/>
       <c r="J24" s="57"/>
@@ -7771,18 +8223,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:37" ht="24" customHeight="1">
-      <c r="B1" s="148" t="s">
-        <v>70</v>
-      </c>
-      <c r="C1" s="148"/>
-      <c r="D1" s="148"/>
-      <c r="E1" s="148"/>
-      <c r="F1" s="148"/>
-      <c r="G1" s="148"/>
-      <c r="H1" s="148"/>
-      <c r="I1" s="148"/>
-      <c r="J1" s="148"/>
-      <c r="K1" s="148"/>
+      <c r="B1" s="102" t="s">
+        <v>74</v>
+      </c>
+      <c r="C1" s="102"/>
+      <c r="D1" s="102"/>
+      <c r="E1" s="102"/>
+      <c r="F1" s="102"/>
+      <c r="G1" s="102"/>
+      <c r="H1" s="102"/>
+      <c r="I1" s="102"/>
+      <c r="J1" s="102"/>
+      <c r="K1" s="102"/>
       <c r="L1" s="63"/>
       <c r="M1" s="63"/>
       <c r="N1" s="63"/>
@@ -7808,7 +8260,7 @@
     </row>
     <row r="3" spans="2:37" ht="15.6" customHeight="1">
       <c r="B3" s="3" t="s">
-        <v>67</v>
+        <v>38</v>
       </c>
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
@@ -7816,7 +8268,7 @@
     </row>
     <row r="4" spans="2:37" ht="15.6" customHeight="1">
       <c r="B4" s="3" t="s">
-        <v>69</v>
+        <v>39</v>
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
@@ -7824,14 +8276,14 @@
     </row>
     <row r="5" spans="2:37" ht="15.6" customHeight="1">
       <c r="B5" s="3" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="C5" s="3"/>
       <c r="D5" s="80">
         <v>46331</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>66</v>
+        <v>41</v>
       </c>
       <c r="G5" s="62"/>
       <c r="H5" s="62"/>
@@ -7855,7 +8307,7 @@
     </row>
     <row r="7" spans="2:37" ht="15.6" customHeight="1">
       <c r="B7" s="73" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="C7" s="74"/>
       <c r="D7" s="74"/>
@@ -7864,7 +8316,7 @@
       <c r="G7" s="74"/>
       <c r="H7" s="74"/>
       <c r="I7" s="74" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="J7" s="74"/>
       <c r="K7" s="74"/>
@@ -7897,13 +8349,13 @@
     </row>
     <row r="8" spans="2:37" s="61" customFormat="1" ht="29.1" customHeight="1">
       <c r="B8" s="72" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C8" s="69" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="D8" s="69" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="E8" s="60"/>
       <c r="F8" s="60"/>
@@ -7918,7 +8370,7 @@
         <v>1</v>
       </c>
       <c r="C9" s="59" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="D9" s="59">
         <v>5</v>
@@ -7972,7 +8424,7 @@
     </row>
     <row r="14" spans="2:37" ht="15.6" customHeight="1">
       <c r="B14" s="73" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="C14" s="74"/>
       <c r="D14" s="74"/>
@@ -8012,28 +8464,28 @@
     </row>
     <row r="15" spans="2:37" ht="35.1" customHeight="1">
       <c r="B15" s="71" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C15" s="71" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="D15" s="71" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="E15" s="71" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="F15" s="77" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="G15" s="69" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="H15" s="71" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="I15" s="71" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="J15" s="1"/>
       <c r="K15" s="1"/>
@@ -8043,25 +8495,25 @@
         <v>1</v>
       </c>
       <c r="C16" s="58" t="s">
+        <v>54</v>
+      </c>
+      <c r="D16" s="58" t="s">
         <v>55</v>
       </c>
-      <c r="D16" s="58" t="s">
+      <c r="E16" s="58" t="s">
         <v>56</v>
       </c>
-      <c r="E16" s="58" t="s">
-        <v>61</v>
-      </c>
       <c r="F16" s="78" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="G16" s="58">
         <v>40</v>
       </c>
       <c r="H16" s="58" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="I16" s="58" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="J16" s="1"/>
       <c r="K16" s="1"/>
@@ -8071,25 +8523,25 @@
         <v>2</v>
       </c>
       <c r="C17" s="58" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D17" s="58" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E17" s="58" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F17" s="81" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G17" s="58">
         <v>32</v>
       </c>
       <c r="H17" s="58" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="I17" s="82" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="J17" s="1"/>
       <c r="K17" s="1"/>
@@ -8099,25 +8551,25 @@
         <v>3</v>
       </c>
       <c r="C18" s="58" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D18" s="58" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="E18" s="58" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F18" s="78" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G18" s="58">
         <v>36</v>
       </c>
       <c r="H18" s="58" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="I18" s="58" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="J18" s="1"/>
       <c r="K18" s="1"/>
@@ -8127,25 +8579,25 @@
         <v>4</v>
       </c>
       <c r="C19" s="58" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D19" s="58" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="E19" s="58" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F19" s="81" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="G19" s="58">
         <v>40</v>
       </c>
       <c r="H19" s="58" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="I19" s="58" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="J19" s="1"/>
       <c r="K19" s="1"/>
@@ -8155,32 +8607,32 @@
         <v>5</v>
       </c>
       <c r="C20" s="58" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D20" s="58" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E20" s="58" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="F20" s="78" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="G20" s="58">
         <v>40</v>
       </c>
       <c r="H20" s="58" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="I20" s="82" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="J20" s="1"/>
       <c r="K20" s="1"/>
     </row>
     <row r="22" spans="1:37" ht="15.6" customHeight="1">
       <c r="B22" s="73" t="s">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="C22" s="74"/>
       <c r="D22" s="74"/>
@@ -8221,28 +8673,28 @@
     <row r="23" spans="1:37" s="67" customFormat="1" ht="15.6" customHeight="1">
       <c r="A23" s="28"/>
       <c r="B23" s="69" t="s">
-        <v>12</v>
-      </c>
-      <c r="C23" s="149" t="s">
-        <v>47</v>
-      </c>
-      <c r="D23" s="153"/>
-      <c r="E23" s="150"/>
-      <c r="F23" s="149" t="s">
-        <v>48</v>
-      </c>
-      <c r="G23" s="150"/>
+        <v>16</v>
+      </c>
+      <c r="C23" s="155" t="s">
+        <v>67</v>
+      </c>
+      <c r="D23" s="159"/>
+      <c r="E23" s="156"/>
+      <c r="F23" s="155" t="s">
+        <v>68</v>
+      </c>
+      <c r="G23" s="156"/>
       <c r="H23" s="70" t="s">
-        <v>49</v>
+        <v>69</v>
       </c>
       <c r="I23" s="69" t="s">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="J23" s="69" t="s">
-        <v>51</v>
+        <v>71</v>
       </c>
       <c r="K23" s="69" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -8255,13 +8707,13 @@
       <c r="B24" s="56">
         <v>1</v>
       </c>
-      <c r="C24" s="145" t="s">
-        <v>53</v>
-      </c>
-      <c r="D24" s="146"/>
-      <c r="E24" s="147"/>
-      <c r="F24" s="151"/>
-      <c r="G24" s="152"/>
+      <c r="C24" s="152" t="s">
+        <v>73</v>
+      </c>
+      <c r="D24" s="153"/>
+      <c r="E24" s="154"/>
+      <c r="F24" s="157"/>
+      <c r="G24" s="158"/>
       <c r="H24" s="68"/>
       <c r="I24" s="57"/>
       <c r="J24" s="57"/>
@@ -8307,18 +8759,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:37" ht="24" customHeight="1">
-      <c r="B1" s="148" t="s">
-        <v>77</v>
-      </c>
-      <c r="C1" s="148"/>
-      <c r="D1" s="148"/>
-      <c r="E1" s="148"/>
-      <c r="F1" s="148"/>
-      <c r="G1" s="148"/>
-      <c r="H1" s="148"/>
-      <c r="I1" s="148"/>
-      <c r="J1" s="148"/>
-      <c r="K1" s="148"/>
+      <c r="B1" s="102" t="s">
+        <v>78</v>
+      </c>
+      <c r="C1" s="102"/>
+      <c r="D1" s="102"/>
+      <c r="E1" s="102"/>
+      <c r="F1" s="102"/>
+      <c r="G1" s="102"/>
+      <c r="H1" s="102"/>
+      <c r="I1" s="102"/>
+      <c r="J1" s="102"/>
+      <c r="K1" s="102"/>
       <c r="L1" s="63"/>
       <c r="M1" s="63"/>
       <c r="N1" s="63"/>
@@ -8344,7 +8796,7 @@
     </row>
     <row r="3" spans="2:37" ht="15.6" customHeight="1">
       <c r="B3" s="3" t="s">
-        <v>67</v>
+        <v>38</v>
       </c>
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
@@ -8352,7 +8804,7 @@
     </row>
     <row r="4" spans="2:37" ht="15.6" customHeight="1">
       <c r="B4" s="3" t="s">
-        <v>69</v>
+        <v>39</v>
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
@@ -8360,14 +8812,14 @@
     </row>
     <row r="5" spans="2:37" ht="15.6" customHeight="1">
       <c r="B5" s="3" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="C5" s="3"/>
       <c r="D5" s="80" t="s">
         <v>79</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>66</v>
+        <v>41</v>
       </c>
       <c r="G5" s="62"/>
       <c r="H5" s="62"/>
@@ -8391,7 +8843,7 @@
     </row>
     <row r="7" spans="2:37" ht="15.6" customHeight="1">
       <c r="B7" s="73" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="C7" s="74"/>
       <c r="D7" s="74"/>
@@ -8400,7 +8852,7 @@
       <c r="G7" s="74"/>
       <c r="H7" s="74"/>
       <c r="I7" s="74" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="J7" s="74"/>
       <c r="K7" s="74"/>
@@ -8433,13 +8885,13 @@
     </row>
     <row r="8" spans="2:37" s="61" customFormat="1" ht="29.1" customHeight="1">
       <c r="B8" s="72" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C8" s="69" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="D8" s="69" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="E8" s="60"/>
       <c r="F8" s="60"/>
@@ -8454,7 +8906,7 @@
         <v>1</v>
       </c>
       <c r="C9" s="59" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="D9" s="59">
         <v>5</v>
@@ -8508,7 +8960,7 @@
     </row>
     <row r="14" spans="2:37" ht="15.6" customHeight="1">
       <c r="B14" s="73" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="C14" s="74"/>
       <c r="D14" s="74"/>
@@ -8548,31 +9000,31 @@
     </row>
     <row r="15" spans="2:37" ht="35.1" customHeight="1">
       <c r="B15" s="71" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C15" s="71" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="D15" s="71" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="E15" s="71" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="F15" s="71" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="G15" s="77" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="H15" s="69" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="I15" s="71" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="J15" s="71" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="K15" s="1"/>
       <c r="L15" s="1"/>
@@ -8582,25 +9034,25 @@
         <v>1</v>
       </c>
       <c r="C16" s="58" t="s">
+        <v>54</v>
+      </c>
+      <c r="D16" s="58" t="s">
         <v>55</v>
       </c>
-      <c r="D16" s="58" t="s">
+      <c r="E16" s="58" t="s">
+        <v>81</v>
+      </c>
+      <c r="F16" s="58" t="s">
         <v>56</v>
       </c>
-      <c r="E16" s="58" t="s">
-        <v>75</v>
-      </c>
-      <c r="F16" s="58" t="s">
-        <v>61</v>
-      </c>
       <c r="G16" s="78" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H16" s="58">
         <v>40</v>
       </c>
       <c r="I16" s="58" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="J16" s="58"/>
       <c r="K16" s="1"/>
@@ -8611,25 +9063,25 @@
         <v>2</v>
       </c>
       <c r="C17" s="58" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D17" s="58" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E17" s="58" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="F17" s="58" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G17" s="83" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="H17" s="58">
         <v>40</v>
       </c>
       <c r="I17" s="58" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="J17" s="82"/>
       <c r="K17" s="1"/>
@@ -8640,25 +9092,25 @@
         <v>3</v>
       </c>
       <c r="C18" s="58" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D18" s="58" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="E18" s="58" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="F18" s="58" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G18" s="78" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H18" s="58">
         <v>36</v>
       </c>
       <c r="I18" s="58" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="J18" s="58"/>
       <c r="K18" s="1"/>
@@ -8669,25 +9121,25 @@
         <v>4</v>
       </c>
       <c r="C19" s="58" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D19" s="58" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="E19" s="58" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="F19" s="58" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G19" s="81" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H19" s="58">
         <v>40</v>
       </c>
       <c r="I19" s="58" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="J19" s="58"/>
       <c r="K19" s="1"/>
@@ -8698,25 +9150,25 @@
         <v>5</v>
       </c>
       <c r="C20" s="58" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D20" s="58" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E20" s="58" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="F20" s="58" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="G20" s="78" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="H20" s="58">
         <v>40</v>
       </c>
       <c r="I20" s="58" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="J20" s="82"/>
       <c r="K20" s="1"/>
@@ -8724,7 +9176,7 @@
     </row>
     <row r="22" spans="1:37" ht="15.6" customHeight="1">
       <c r="B22" s="73" t="s">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="C22" s="74"/>
       <c r="D22" s="74"/>
@@ -8765,28 +9217,28 @@
     <row r="23" spans="1:37" s="67" customFormat="1" ht="15.6" customHeight="1">
       <c r="A23" s="28"/>
       <c r="B23" s="69" t="s">
-        <v>12</v>
-      </c>
-      <c r="C23" s="149" t="s">
-        <v>47</v>
-      </c>
-      <c r="D23" s="153"/>
-      <c r="E23" s="150"/>
-      <c r="F23" s="149" t="s">
-        <v>48</v>
-      </c>
-      <c r="G23" s="150"/>
+        <v>16</v>
+      </c>
+      <c r="C23" s="155" t="s">
+        <v>67</v>
+      </c>
+      <c r="D23" s="159"/>
+      <c r="E23" s="156"/>
+      <c r="F23" s="155" t="s">
+        <v>68</v>
+      </c>
+      <c r="G23" s="156"/>
       <c r="H23" s="70" t="s">
-        <v>49</v>
+        <v>69</v>
       </c>
       <c r="I23" s="69" t="s">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="J23" s="69" t="s">
-        <v>51</v>
+        <v>71</v>
       </c>
       <c r="K23" s="69" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -8799,13 +9251,13 @@
       <c r="B24" s="56">
         <v>1</v>
       </c>
-      <c r="C24" s="145" t="s">
-        <v>53</v>
-      </c>
-      <c r="D24" s="146"/>
-      <c r="E24" s="147"/>
-      <c r="F24" s="151"/>
-      <c r="G24" s="152"/>
+      <c r="C24" s="152" t="s">
+        <v>73</v>
+      </c>
+      <c r="D24" s="153"/>
+      <c r="E24" s="154"/>
+      <c r="F24" s="157"/>
+      <c r="G24" s="158"/>
       <c r="H24" s="68"/>
       <c r="I24" s="57"/>
       <c r="J24" s="57"/>
@@ -8851,18 +9303,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:37" ht="24" customHeight="1">
-      <c r="B1" s="148" t="s">
-        <v>81</v>
-      </c>
-      <c r="C1" s="148"/>
-      <c r="D1" s="148"/>
-      <c r="E1" s="148"/>
-      <c r="F1" s="148"/>
-      <c r="G1" s="148"/>
-      <c r="H1" s="148"/>
-      <c r="I1" s="148"/>
-      <c r="J1" s="148"/>
-      <c r="K1" s="148"/>
+      <c r="B1" s="102" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1" s="102"/>
+      <c r="D1" s="102"/>
+      <c r="E1" s="102"/>
+      <c r="F1" s="102"/>
+      <c r="G1" s="102"/>
+      <c r="H1" s="102"/>
+      <c r="I1" s="102"/>
+      <c r="J1" s="102"/>
+      <c r="K1" s="102"/>
       <c r="L1" s="63"/>
       <c r="M1" s="63"/>
       <c r="N1" s="63"/>
@@ -8888,7 +9340,7 @@
     </row>
     <row r="3" spans="2:37" ht="15.6" customHeight="1">
       <c r="B3" s="3" t="s">
-        <v>67</v>
+        <v>38</v>
       </c>
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
@@ -8896,7 +9348,7 @@
     </row>
     <row r="4" spans="2:37" ht="15.6" customHeight="1">
       <c r="B4" s="3" t="s">
-        <v>69</v>
+        <v>39</v>
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
@@ -8904,14 +9356,14 @@
     </row>
     <row r="5" spans="2:37" ht="15.6" customHeight="1">
       <c r="B5" s="3" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="C5" s="3"/>
       <c r="D5" s="80" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>66</v>
+        <v>41</v>
       </c>
       <c r="G5" s="62"/>
       <c r="H5" s="62"/>
@@ -8935,7 +9387,7 @@
     </row>
     <row r="7" spans="2:37" ht="15.6" customHeight="1">
       <c r="B7" s="73" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="C7" s="74"/>
       <c r="D7" s="74"/>
@@ -8944,7 +9396,7 @@
       <c r="G7" s="74"/>
       <c r="H7" s="74"/>
       <c r="I7" s="74" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="J7" s="74"/>
       <c r="K7" s="74"/>
@@ -8977,13 +9429,13 @@
     </row>
     <row r="8" spans="2:37" s="61" customFormat="1" ht="29.1" customHeight="1">
       <c r="B8" s="72" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C8" s="69" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="D8" s="69" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="E8" s="60"/>
       <c r="F8" s="60"/>
@@ -8998,7 +9450,7 @@
         <v>1</v>
       </c>
       <c r="C9" s="59" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="D9" s="59">
         <v>5</v>
@@ -9052,7 +9504,7 @@
     </row>
     <row r="14" spans="2:37" ht="15.6" customHeight="1">
       <c r="B14" s="73" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="C14" s="74"/>
       <c r="D14" s="74"/>
@@ -9092,31 +9544,31 @@
     </row>
     <row r="15" spans="2:37" ht="35.1" customHeight="1">
       <c r="B15" s="71" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C15" s="71" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="D15" s="71" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="E15" s="71" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="F15" s="71" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="G15" s="77" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="H15" s="69" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="I15" s="71" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="J15" s="71" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="K15" s="1"/>
       <c r="L15" s="1"/>
@@ -9126,25 +9578,25 @@
         <v>1</v>
       </c>
       <c r="C16" s="58" t="s">
+        <v>54</v>
+      </c>
+      <c r="D16" s="58" t="s">
         <v>55</v>
       </c>
-      <c r="D16" s="58" t="s">
+      <c r="E16" s="58" t="s">
+        <v>81</v>
+      </c>
+      <c r="F16" s="58" t="s">
         <v>56</v>
       </c>
-      <c r="E16" s="58" t="s">
-        <v>75</v>
-      </c>
-      <c r="F16" s="58" t="s">
-        <v>61</v>
-      </c>
       <c r="G16" s="78" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H16" s="58">
         <v>40</v>
       </c>
       <c r="I16" s="58" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="J16" s="58"/>
       <c r="K16" s="1"/>
@@ -9155,25 +9607,25 @@
         <v>2</v>
       </c>
       <c r="C17" s="58" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D17" s="58" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E17" s="58" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="F17" s="58" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G17" s="83" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="H17" s="58">
         <v>40</v>
       </c>
       <c r="I17" s="58" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="J17" s="82"/>
       <c r="K17" s="1"/>
@@ -9184,25 +9636,25 @@
         <v>3</v>
       </c>
       <c r="C18" s="58" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D18" s="58" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="E18" s="58" t="s">
+        <v>81</v>
+      </c>
+      <c r="F18" s="58" t="s">
+        <v>60</v>
+      </c>
+      <c r="G18" s="78" t="s">
         <v>75</v>
-      </c>
-      <c r="F18" s="58" t="s">
-        <v>62</v>
-      </c>
-      <c r="G18" s="78" t="s">
-        <v>71</v>
       </c>
       <c r="H18" s="58">
         <v>40</v>
       </c>
       <c r="I18" s="58" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="J18" s="58"/>
       <c r="K18" s="1"/>
@@ -9213,25 +9665,25 @@
         <v>4</v>
       </c>
       <c r="C19" s="58" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D19" s="58" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="E19" s="58" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="F19" s="58" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G19" s="81" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H19" s="58">
         <v>40</v>
       </c>
       <c r="I19" s="58" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="J19" s="58"/>
       <c r="K19" s="1"/>
@@ -9242,25 +9694,25 @@
         <v>5</v>
       </c>
       <c r="C20" s="58" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D20" s="58" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E20" s="58" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="F20" s="58" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="G20" s="78" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H20" s="58">
         <v>40</v>
       </c>
       <c r="I20" s="58" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="J20" s="82"/>
       <c r="K20" s="1"/>
@@ -9268,7 +9720,7 @@
     </row>
     <row r="22" spans="1:37" ht="15.6" customHeight="1">
       <c r="B22" s="73" t="s">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="C22" s="74"/>
       <c r="D22" s="74"/>
@@ -9309,28 +9761,28 @@
     <row r="23" spans="1:37" s="67" customFormat="1" ht="15.6" customHeight="1">
       <c r="A23" s="28"/>
       <c r="B23" s="69" t="s">
-        <v>12</v>
-      </c>
-      <c r="C23" s="149" t="s">
-        <v>47</v>
-      </c>
-      <c r="D23" s="153"/>
-      <c r="E23" s="150"/>
-      <c r="F23" s="149" t="s">
-        <v>48</v>
-      </c>
-      <c r="G23" s="150"/>
+        <v>16</v>
+      </c>
+      <c r="C23" s="155" t="s">
+        <v>67</v>
+      </c>
+      <c r="D23" s="159"/>
+      <c r="E23" s="156"/>
+      <c r="F23" s="155" t="s">
+        <v>68</v>
+      </c>
+      <c r="G23" s="156"/>
       <c r="H23" s="70" t="s">
-        <v>49</v>
+        <v>69</v>
       </c>
       <c r="I23" s="69" t="s">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="J23" s="69" t="s">
-        <v>51</v>
+        <v>71</v>
       </c>
       <c r="K23" s="69" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -9343,13 +9795,13 @@
       <c r="B24" s="56">
         <v>1</v>
       </c>
-      <c r="C24" s="145" t="s">
-        <v>53</v>
-      </c>
-      <c r="D24" s="146"/>
-      <c r="E24" s="147"/>
-      <c r="F24" s="151"/>
-      <c r="G24" s="152"/>
+      <c r="C24" s="152" t="s">
+        <v>73</v>
+      </c>
+      <c r="D24" s="153"/>
+      <c r="E24" s="154"/>
+      <c r="F24" s="157"/>
+      <c r="G24" s="158"/>
       <c r="H24" s="68"/>
       <c r="I24" s="57"/>
       <c r="J24" s="57"/>
@@ -9395,18 +9847,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:37" ht="24" customHeight="1">
-      <c r="B1" s="148" t="s">
-        <v>82</v>
-      </c>
-      <c r="C1" s="148"/>
-      <c r="D1" s="148"/>
-      <c r="E1" s="148"/>
-      <c r="F1" s="148"/>
-      <c r="G1" s="148"/>
-      <c r="H1" s="148"/>
-      <c r="I1" s="148"/>
-      <c r="J1" s="148"/>
-      <c r="K1" s="148"/>
+      <c r="B1" s="102" t="s">
+        <v>86</v>
+      </c>
+      <c r="C1" s="102"/>
+      <c r="D1" s="102"/>
+      <c r="E1" s="102"/>
+      <c r="F1" s="102"/>
+      <c r="G1" s="102"/>
+      <c r="H1" s="102"/>
+      <c r="I1" s="102"/>
+      <c r="J1" s="102"/>
+      <c r="K1" s="102"/>
       <c r="L1" s="63"/>
       <c r="M1" s="63"/>
       <c r="N1" s="63"/>
@@ -9432,7 +9884,7 @@
     </row>
     <row r="3" spans="2:37" ht="15.6" customHeight="1">
       <c r="B3" s="3" t="s">
-        <v>67</v>
+        <v>38</v>
       </c>
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
@@ -9440,7 +9892,7 @@
     </row>
     <row r="4" spans="2:37" ht="15.6" customHeight="1">
       <c r="B4" s="3" t="s">
-        <v>69</v>
+        <v>39</v>
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
@@ -9448,14 +9900,14 @@
     </row>
     <row r="5" spans="2:37" ht="15.6" customHeight="1">
       <c r="B5" s="3" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="C5" s="3"/>
       <c r="D5" s="80">
         <v>46059</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>66</v>
+        <v>41</v>
       </c>
       <c r="G5" s="62"/>
       <c r="H5" s="62"/>
@@ -9479,7 +9931,7 @@
     </row>
     <row r="7" spans="2:37" ht="15.6" customHeight="1">
       <c r="B7" s="73" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="C7" s="74"/>
       <c r="D7" s="74"/>
@@ -9488,7 +9940,7 @@
       <c r="G7" s="74"/>
       <c r="H7" s="74"/>
       <c r="I7" s="74" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="J7" s="74"/>
       <c r="K7" s="74"/>
@@ -9521,13 +9973,13 @@
     </row>
     <row r="8" spans="2:37" s="61" customFormat="1" ht="29.1" customHeight="1">
       <c r="B8" s="72" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C8" s="69" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="D8" s="69" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="E8" s="60"/>
       <c r="F8" s="60"/>
@@ -9542,7 +9994,7 @@
         <v>1</v>
       </c>
       <c r="C9" s="59" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="D9" s="59">
         <v>5</v>
@@ -9596,7 +10048,7 @@
     </row>
     <row r="14" spans="2:37" ht="15.6" customHeight="1">
       <c r="B14" s="73" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="C14" s="74"/>
       <c r="D14" s="74"/>
@@ -9636,31 +10088,31 @@
     </row>
     <row r="15" spans="2:37" ht="35.1" customHeight="1">
       <c r="B15" s="71" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C15" s="71" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="D15" s="71" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="E15" s="71" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="F15" s="71" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="G15" s="77" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="H15" s="69" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="I15" s="71" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="J15" s="71" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="K15" s="1"/>
       <c r="L15" s="1"/>
@@ -9670,25 +10122,25 @@
         <v>1</v>
       </c>
       <c r="C16" s="58" t="s">
+        <v>54</v>
+      </c>
+      <c r="D16" s="58" t="s">
         <v>55</v>
       </c>
-      <c r="D16" s="58" t="s">
+      <c r="E16" s="58" t="s">
+        <v>81</v>
+      </c>
+      <c r="F16" s="58" t="s">
         <v>56</v>
       </c>
-      <c r="E16" s="58" t="s">
-        <v>75</v>
-      </c>
-      <c r="F16" s="58" t="s">
-        <v>61</v>
-      </c>
       <c r="G16" s="78" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H16" s="58">
         <v>40</v>
       </c>
       <c r="I16" s="58" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="J16" s="58"/>
       <c r="K16" s="1"/>
@@ -9699,25 +10151,25 @@
         <v>2</v>
       </c>
       <c r="C17" s="58" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D17" s="58" t="s">
+        <v>59</v>
+      </c>
+      <c r="E17" s="58" t="s">
+        <v>82</v>
+      </c>
+      <c r="F17" s="58" t="s">
+        <v>60</v>
+      </c>
+      <c r="G17" s="83" t="s">
         <v>57</v>
-      </c>
-      <c r="E17" s="58" t="s">
-        <v>76</v>
-      </c>
-      <c r="F17" s="58" t="s">
-        <v>62</v>
-      </c>
-      <c r="G17" s="83" t="s">
-        <v>63</v>
       </c>
       <c r="H17" s="58">
         <v>40</v>
       </c>
       <c r="I17" s="58" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="J17" s="82"/>
       <c r="K17" s="1"/>
@@ -9728,25 +10180,25 @@
         <v>3</v>
       </c>
       <c r="C18" s="58" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D18" s="58" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="E18" s="58" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="F18" s="58" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G18" s="78" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="H18" s="58">
         <v>40</v>
       </c>
       <c r="I18" s="58" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="J18" s="58"/>
       <c r="K18" s="1"/>
@@ -9757,25 +10209,25 @@
         <v>4</v>
       </c>
       <c r="C19" s="58" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D19" s="58" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="E19" s="58" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="F19" s="58" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G19" s="81" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H19" s="58">
         <v>40</v>
       </c>
       <c r="I19" s="58" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="J19" s="58"/>
       <c r="K19" s="1"/>
@@ -9786,25 +10238,25 @@
         <v>5</v>
       </c>
       <c r="C20" s="58" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D20" s="58" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E20" s="58" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="F20" s="58" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="G20" s="78" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H20" s="58">
         <v>40</v>
       </c>
       <c r="I20" s="58" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="J20" s="82"/>
       <c r="K20" s="1"/>
@@ -9812,7 +10264,7 @@
     </row>
     <row r="22" spans="1:37" ht="15.6" customHeight="1">
       <c r="B22" s="73" t="s">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="C22" s="74"/>
       <c r="D22" s="74"/>
@@ -9853,28 +10305,28 @@
     <row r="23" spans="1:37" s="67" customFormat="1" ht="15.6" customHeight="1">
       <c r="A23" s="28"/>
       <c r="B23" s="69" t="s">
-        <v>12</v>
-      </c>
-      <c r="C23" s="149" t="s">
-        <v>47</v>
-      </c>
-      <c r="D23" s="153"/>
-      <c r="E23" s="150"/>
-      <c r="F23" s="149" t="s">
-        <v>48</v>
-      </c>
-      <c r="G23" s="150"/>
+        <v>16</v>
+      </c>
+      <c r="C23" s="155" t="s">
+        <v>67</v>
+      </c>
+      <c r="D23" s="159"/>
+      <c r="E23" s="156"/>
+      <c r="F23" s="155" t="s">
+        <v>68</v>
+      </c>
+      <c r="G23" s="156"/>
       <c r="H23" s="70" t="s">
-        <v>49</v>
+        <v>69</v>
       </c>
       <c r="I23" s="69" t="s">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="J23" s="69" t="s">
-        <v>51</v>
+        <v>71</v>
       </c>
       <c r="K23" s="69" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -9887,13 +10339,13 @@
       <c r="B24" s="56">
         <v>1</v>
       </c>
-      <c r="C24" s="145" t="s">
-        <v>53</v>
-      </c>
-      <c r="D24" s="146"/>
-      <c r="E24" s="147"/>
-      <c r="F24" s="151"/>
-      <c r="G24" s="152"/>
+      <c r="C24" s="152" t="s">
+        <v>73</v>
+      </c>
+      <c r="D24" s="153"/>
+      <c r="E24" s="154"/>
+      <c r="F24" s="157"/>
+      <c r="G24" s="158"/>
       <c r="H24" s="68"/>
       <c r="I24" s="57"/>
       <c r="J24" s="57"/>
@@ -9939,18 +10391,18 @@
   <sheetData>
     <row r="1" spans="1:11" ht="25.5">
       <c r="A1" s="2"/>
-      <c r="B1" s="148" t="s">
-        <v>83</v>
-      </c>
-      <c r="C1" s="148"/>
-      <c r="D1" s="148"/>
-      <c r="E1" s="148"/>
-      <c r="F1" s="148"/>
-      <c r="G1" s="148"/>
-      <c r="H1" s="148"/>
-      <c r="I1" s="148"/>
-      <c r="J1" s="148"/>
-      <c r="K1" s="148"/>
+      <c r="B1" s="102" t="s">
+        <v>87</v>
+      </c>
+      <c r="C1" s="102"/>
+      <c r="D1" s="102"/>
+      <c r="E1" s="102"/>
+      <c r="F1" s="102"/>
+      <c r="G1" s="102"/>
+      <c r="H1" s="102"/>
+      <c r="I1" s="102"/>
+      <c r="J1" s="102"/>
+      <c r="K1" s="102"/>
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2"/>
@@ -9968,7 +10420,7 @@
     <row r="3" spans="1:11">
       <c r="A3" s="2"/>
       <c r="B3" s="3" t="s">
-        <v>67</v>
+        <v>38</v>
       </c>
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
@@ -9983,7 +10435,7 @@
     <row r="4" spans="1:11">
       <c r="A4" s="2"/>
       <c r="B4" s="3" t="s">
-        <v>69</v>
+        <v>39</v>
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
@@ -9998,14 +10450,14 @@
     <row r="5" spans="1:11">
       <c r="A5" s="2"/>
       <c r="B5" s="3" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="C5" s="3"/>
       <c r="D5" s="80">
         <v>46240</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>66</v>
+        <v>41</v>
       </c>
       <c r="F5" s="75"/>
       <c r="G5" s="62"/>
@@ -10030,7 +10482,7 @@
     <row r="7" spans="1:11" ht="15.75">
       <c r="A7" s="2"/>
       <c r="B7" s="73" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="C7" s="74"/>
       <c r="D7" s="74"/>
@@ -10039,7 +10491,7 @@
       <c r="G7" s="74"/>
       <c r="H7" s="74"/>
       <c r="I7" s="74" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="J7" s="74"/>
       <c r="K7" s="74"/>
@@ -10047,13 +10499,13 @@
     <row r="8" spans="1:11" ht="25.5">
       <c r="A8" s="61"/>
       <c r="B8" s="72" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C8" s="69" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="D8" s="69" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="E8" s="60"/>
       <c r="F8" s="60"/>
@@ -10069,7 +10521,7 @@
         <v>1</v>
       </c>
       <c r="C9" s="59" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="D9" s="59">
         <v>5</v>
@@ -10137,7 +10589,7 @@
     <row r="14" spans="1:11" ht="15.75">
       <c r="A14" s="2"/>
       <c r="B14" s="73" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="C14" s="74"/>
       <c r="D14" s="74"/>
@@ -10152,31 +10604,31 @@
     <row r="15" spans="1:11" ht="38.25">
       <c r="A15" s="2"/>
       <c r="B15" s="71" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C15" s="71" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="D15" s="71" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="E15" s="71" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="F15" s="71" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="G15" s="77" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="H15" s="69" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="I15" s="71" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="J15" s="71" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="K15" s="1"/>
     </row>
@@ -10186,25 +10638,25 @@
         <v>1</v>
       </c>
       <c r="C16" s="58" t="s">
+        <v>54</v>
+      </c>
+      <c r="D16" s="58" t="s">
         <v>55</v>
       </c>
-      <c r="D16" s="58" t="s">
+      <c r="E16" s="58" t="s">
+        <v>81</v>
+      </c>
+      <c r="F16" s="58" t="s">
         <v>56</v>
       </c>
-      <c r="E16" s="58" t="s">
-        <v>75</v>
-      </c>
-      <c r="F16" s="58" t="s">
-        <v>61</v>
-      </c>
       <c r="G16" s="78" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="H16" s="58">
         <v>40</v>
       </c>
       <c r="I16" s="58" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="J16" s="58"/>
       <c r="K16" s="1"/>
@@ -10215,25 +10667,25 @@
         <v>2</v>
       </c>
       <c r="C17" s="58" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D17" s="58" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E17" s="58" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="F17" s="58" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G17" s="83" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H17" s="58">
         <v>32</v>
       </c>
       <c r="I17" s="58" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="J17" s="82"/>
       <c r="K17" s="1"/>
@@ -10244,25 +10696,25 @@
         <v>3</v>
       </c>
       <c r="C18" s="58" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D18" s="58" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="E18" s="58" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="F18" s="58" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G18" s="78" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="H18" s="58">
         <v>40</v>
       </c>
       <c r="I18" s="58" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="J18" s="58"/>
       <c r="K18" s="1"/>
@@ -10273,25 +10725,25 @@
         <v>4</v>
       </c>
       <c r="C19" s="58" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D19" s="58" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="E19" s="58" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="F19" s="58" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G19" s="81" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="H19" s="58">
         <v>40</v>
       </c>
       <c r="I19" s="58" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="J19" s="58"/>
       <c r="K19" s="1"/>
@@ -10302,25 +10754,25 @@
         <v>5</v>
       </c>
       <c r="C20" s="58" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D20" s="58" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E20" s="58" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="F20" s="58" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="G20" s="78" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H20" s="58">
         <v>36</v>
       </c>
       <c r="I20" s="58" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="J20" s="82"/>
       <c r="K20" s="1"/>
@@ -10341,7 +10793,7 @@
     <row r="22" spans="1:11" ht="15.75">
       <c r="A22" s="2"/>
       <c r="B22" s="73" t="s">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="C22" s="74"/>
       <c r="D22" s="74"/>
@@ -10356,28 +10808,28 @@
     <row r="23" spans="1:11" ht="25.5">
       <c r="A23" s="28"/>
       <c r="B23" s="69" t="s">
-        <v>12</v>
-      </c>
-      <c r="C23" s="149" t="s">
-        <v>47</v>
-      </c>
-      <c r="D23" s="153"/>
-      <c r="E23" s="150"/>
-      <c r="F23" s="149" t="s">
-        <v>48</v>
-      </c>
-      <c r="G23" s="150"/>
+        <v>16</v>
+      </c>
+      <c r="C23" s="155" t="s">
+        <v>67</v>
+      </c>
+      <c r="D23" s="159"/>
+      <c r="E23" s="156"/>
+      <c r="F23" s="155" t="s">
+        <v>68</v>
+      </c>
+      <c r="G23" s="156"/>
       <c r="H23" s="70" t="s">
-        <v>49</v>
+        <v>69</v>
       </c>
       <c r="I23" s="69" t="s">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="J23" s="69" t="s">
-        <v>51</v>
+        <v>71</v>
       </c>
       <c r="K23" s="69" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -10385,13 +10837,13 @@
       <c r="B24" s="56">
         <v>1</v>
       </c>
-      <c r="C24" s="145" t="s">
-        <v>53</v>
-      </c>
-      <c r="D24" s="146"/>
-      <c r="E24" s="147"/>
-      <c r="F24" s="151"/>
-      <c r="G24" s="152"/>
+      <c r="C24" s="152" t="s">
+        <v>73</v>
+      </c>
+      <c r="D24" s="153"/>
+      <c r="E24" s="154"/>
+      <c r="F24" s="157"/>
+      <c r="G24" s="158"/>
       <c r="H24" s="68"/>
       <c r="I24" s="57"/>
       <c r="J24" s="57"/>
@@ -10413,17 +10865,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="85f1826d-7539-4f20-bc56-82ada4c604b1" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="e798e13c-2a3f-4e3b-94e5-919099c3ae9d">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010006DFE9B4275FC84B86BBF46966CFCC7A" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="deaedf44f02c972e71a0997a33b53593">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="85f1826d-7539-4f20-bc56-82ada4c604b1" xmlns:ns3="e798e13c-2a3f-4e3b-94e5-919099c3ae9d" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0a73169b8c6d1db1eb325bd8d79b3c23" ns2:_="" ns3:_="">
     <xsd:import namespace="85f1826d-7539-4f20-bc56-82ada4c604b1"/>
@@ -10664,6 +11105,17 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="85f1826d-7539-4f20-bc56-82ada4c604b1" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="e798e13c-2a3f-4e3b-94e5-919099c3ae9d">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -10674,39 +11126,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E6A3FF58-1C0B-461D-938A-F92F6B318FC9}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="85f1826d-7539-4f20-bc56-82ada4c604b1"/>
-    <ds:schemaRef ds:uri="e798e13c-2a3f-4e3b-94e5-919099c3ae9d"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{91961711-E6FE-4D95-A3E0-AA3BF22BE6AF}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{91961711-E6FE-4D95-A3E0-AA3BF22BE6AF}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="85f1826d-7539-4f20-bc56-82ada4c604b1"/>
-    <ds:schemaRef ds:uri="e798e13c-2a3f-4e3b-94e5-919099c3ae9d"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E6A3FF58-1C0B-461D-938A-F92F6B318FC9}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2C0A48DF-A0FE-452D-B130-0AA3484CCFF8}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2C0A48DF-A0FE-452D-B130-0AA3484CCFF8}"/>
 </file>